--- a/results/part3_weights_shap/shap_values.xlsx
+++ b/results/part3_weights_shap/shap_values.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SHAP_VALUES" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SHAP_WEIGHTS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="shap_values" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:F284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -425,2934 +424,6254 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Eyebrow</t>
+          <t>VAS-eyebrow</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Eye</t>
+          <t>VAS-eye</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Nose</t>
+          <t>VAS-nose</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mouth</t>
+          <t>VAS-mouth</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Facial Contour</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>VAS-global</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Tree-Prediction</t>
+          <t>VAS-facial contour</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FA0001</t>
+          <t>1.对称轴133张/丁兰.JPG</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03526951891693861</v>
+        <v>1.369956978119214</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1732709749984195</v>
+        <v>0.7620485111346513</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1284408131567573</v>
+        <v>-0.2328438372871213</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2196170302215732</v>
+        <v>14.31013853343789</v>
       </c>
       <c r="F2" t="n">
-        <v>10.33143986979573</v>
-      </c>
-      <c r="G2" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>60.11901292375922</v>
+        <v>-2.398896769621196</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FA0002</t>
+          <t>1.对称轴133张/丁柯文.JPG</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.4165573169245832</v>
+        <v>-1.715296463300342</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2207045462655756</v>
+        <v>-2.888881283282029</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02214093254517815</v>
+        <v>-2.558701797051091</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.03733377750382047</v>
+        <v>-4.584703509101736</v>
       </c>
       <c r="F3" t="n">
-        <v>15.69213704639546</v>
-      </c>
-      <c r="G3" t="n">
-        <v>65</v>
-      </c>
-      <c r="H3" t="n">
-        <v>65.05860809744449</v>
+        <v>4.58465313518517</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FA0003</t>
+          <t>1.对称轴133张/丁琳玲.JPG</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.220651532591944</v>
+        <v>-0.2372101100236195</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1831984720189645</v>
+        <v>-0.7106890393255936</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1755681138307299</v>
+        <v>0.4157778191989256</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.03179943745219457</v>
+        <v>-10.2881683805342</v>
       </c>
       <c r="F4" t="n">
-        <v>8.661846957760407</v>
-      </c>
-      <c r="G4" t="n">
-        <v>56.75</v>
-      </c>
-      <c r="H4" t="n">
-        <v>57.34567924023266</v>
+        <v>-13.9551402068655</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FA0004</t>
+          <t>1.对称轴133张/丰羽辰.JPG</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3701573621771797</v>
+        <v>-0.3832277571199365</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0488929926869744</v>
+        <v>-1.262763161273042</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2066833883509015</v>
+        <v>-1.821183845066443</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06905877747888425</v>
+        <v>-9.350176692915426</v>
       </c>
       <c r="F5" t="n">
-        <v>1.400274532694372</v>
-      </c>
-      <c r="G5" t="n">
-        <v>52</v>
-      </c>
-      <c r="H5" t="n">
-        <v>50.93226899570063</v>
+        <v>-1.309745127841859</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FA0005</t>
+          <t>1.对称轴133张/代凌旖.JPG</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1655790585059069</v>
+        <v>0.2247611520527608</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2403789102869709</v>
+        <v>0.2179899327424144</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06317875112665906</v>
+        <v>-0.6374385559954763</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09170309599582957</v>
+        <v>9.548761748440098</v>
       </c>
       <c r="F6" t="n">
-        <v>15.79719015515468</v>
-      </c>
-      <c r="G6" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>65.60438852072491</v>
+        <v>-11.04783752812325</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FA0006</t>
+          <t>1.对称轴133张/代四琼.JPG</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.578287421832955</v>
+        <v>-0.2096797073874524</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.26674732444011</v>
+        <v>0.3438015600199757</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.01556322747102387</v>
+        <v>-1.052640957260803</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01491092047186233</v>
+        <v>-3.34721406704662</v>
       </c>
       <c r="F7" t="n">
-        <v>-10.94050001281854</v>
-      </c>
-      <c r="G7" t="n">
-        <v>34</v>
-      </c>
-      <c r="H7" t="n">
-        <v>36.79132960057589</v>
+        <v>-3.525530079208499</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FA0007</t>
+          <t>1.对称轴133张/代玉婷.JPG</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.77711032870653</v>
+        <v>0.7975592549212862</v>
       </c>
       <c r="C8" t="n">
-        <v>0.08412003006689384</v>
+        <v>0.9561051478917351</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1289245324857951</v>
+        <v>0.683538964865313</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4467143316956874</v>
+        <v>-2.530777657490196</v>
       </c>
       <c r="F8" t="n">
-        <v>25.47109195429377</v>
-      </c>
-      <c r="G8" t="n">
-        <v>78</v>
-      </c>
-      <c r="H8" t="n">
-        <v>77.48547784391539</v>
+        <v>-3.938522294404876</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FA0008</t>
+          <t>1.对称轴133张/代芯妮.JPG</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.615024573786174</v>
+        <v>2.292571238097711</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1497335628163435</v>
+        <v>0.9097026784886618</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0186847875032057</v>
+        <v>-1.36695742771002</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0005810828752826061</v>
+        <v>-2.60536478099889</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9565001824228174</v>
-      </c>
-      <c r="G9" t="n">
-        <v>48.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>49.74999284210849</v>
+        <v>-0.4453816254274997</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FA0009</t>
+          <t>1.对称轴133张/党琪越.JPG</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.9392931363410709</v>
+        <v>-0.5490055297224761</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.07310496847940055</v>
+        <v>-2.890888519066762</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01352288335336396</v>
+        <v>1.988391150149955</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0322041982713093</v>
+        <v>-4.650877892497323</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.719060287333434</v>
-      </c>
-      <c r="G10" t="n">
-        <v>42</v>
-      </c>
-      <c r="H10" t="n">
-        <v>40.8917853561374</v>
+        <v>4.232784206919791</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FA0010</t>
+          <t>1.对称轴133张/刁聪.JPG</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.733033531421888</v>
+        <v>-0.6374698545233793</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1054494336222945</v>
+        <v>-0.9050581978875847</v>
       </c>
       <c r="D11" t="n">
-        <v>0.06933677069742906</v>
+        <v>1.546378549469048</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4022615639207163</v>
+        <v>-1.583121501333919</v>
       </c>
       <c r="F11" t="n">
-        <v>37.4423378802318</v>
-      </c>
-      <c r="G11" t="n">
-        <v>100</v>
-      </c>
-      <c r="H11" t="n">
-        <v>90.32993584656086</v>
+        <v>-0.4086589132742107</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FA0011</t>
+          <t>1.对称轴133张/崔力坤.JPG</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.8276266005451084</v>
+        <v>-1.45411888140736</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1680649134321809</v>
+        <v>-2.43049415216174</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1011502218105251</v>
+        <v>-1.932276467860045</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06531094040646812</v>
+        <v>-9.03074406846412</v>
       </c>
       <c r="F12" t="n">
-        <v>30.23864291789786</v>
-      </c>
-      <c r="G12" t="n">
-        <v>78.75</v>
-      </c>
-      <c r="H12" t="n">
-        <v>78.98692923280424</v>
+        <v>-11.71696301432343</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FA0012</t>
+          <t>1.对称轴133张/巴比诺.JPG</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.194463640939791</v>
+        <v>2.884334393448885</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.01714153530039655</v>
+        <v>4.035229768782107</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01351370772224107</v>
+        <v>0.07921228963667183</v>
       </c>
       <c r="E13" t="n">
-        <v>0.04161136735897298</v>
+        <v>-3.471142986210535</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.049480231650748</v>
-      </c>
-      <c r="G13" t="n">
-        <v>46</v>
-      </c>
-      <c r="H13" t="n">
-        <v>44.7604836157365</v>
+        <v>14.83443661679269</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FA0013</t>
+          <t>1.对称轴133张/德吉龙珍.JPG</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.7006550487255813</v>
+        <v>-0.4233052632053416</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.09180228447392644</v>
+        <v>1.516047569080912</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0898062945375173</v>
+        <v>0.4796435604776937</v>
       </c>
       <c r="E14" t="n">
-        <v>0.04738646565616468</v>
+        <v>4.128747160162911</v>
       </c>
       <c r="F14" t="n">
-        <v>20.94705115667002</v>
-      </c>
-      <c r="G14" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="H14" t="n">
-        <v>69.8693032503308</v>
+        <v>15.10343705593365</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FA0014</t>
+          <t>1.对称轴133张/戴昀纭.JPG</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.9445396547238375</v>
+        <v>-0.4338483538800374</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.2492577549765053</v>
+        <v>-2.081921201884134</v>
       </c>
       <c r="D15" t="n">
-        <v>0.02388397869459368</v>
+        <v>1.536807427231784</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.05514762343124564</v>
+        <v>-1.272355851359478</v>
       </c>
       <c r="F15" t="n">
-        <v>3.256294215350483</v>
-      </c>
-      <c r="G15" t="n">
-        <v>51.25</v>
-      </c>
-      <c r="H15" t="n">
-        <v>51.60874982758016</v>
+        <v>-8.172445270991538</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FA0015</t>
+          <t>1.对称轴133张/戴瑜宸.JPG</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.4402900737625572</v>
+        <v>-0.651924629515393</v>
       </c>
       <c r="C16" t="n">
-        <v>0.02730095514475667</v>
+        <v>-2.141850095572327</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3713233010700946</v>
+        <v>-2.481229288675288</v>
       </c>
       <c r="E16" t="n">
-        <v>0.02915246172675819</v>
+        <v>-10.56050583420997</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.982592888545197</v>
-      </c>
-      <c r="G16" t="n">
-        <v>44</v>
-      </c>
-      <c r="H16" t="n">
-        <v>42.83976382016034</v>
+        <v>-10.95575340291049</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FA0016</t>
+          <t>1.对称轴133张/方利.JPG</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.1612930252976209</v>
+        <v>-0.5948684517878332</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1911590000780705</v>
+        <v>0.4425676555604149</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.002386663181109665</v>
+        <v>-0.5902623551778354</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07031904139439903</v>
+        <v>9.170840376469584</v>
       </c>
       <c r="F17" t="n">
-        <v>17.48711515467231</v>
-      </c>
-      <c r="G17" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="H17" t="n">
-        <v>67.16243017433273</v>
+        <v>8.867126190718755</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FA0017</t>
+          <t>1.对称轴133张/方媛.JPG</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.738352281158285</v>
+        <v>-0.05880288925023028</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.08988330902425148</v>
+        <v>-2.452791716769544</v>
       </c>
       <c r="D18" t="n">
-        <v>0.04222382435428254</v>
+        <v>-1.970982417456441</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02531704263320942</v>
+        <v>-10.54202526086419</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7877086643904074</v>
-      </c>
-      <c r="G18" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="H18" t="n">
-        <v>51.50581784139781</v>
+        <v>-13.75166096654272</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FA0018</t>
+          <t>1.对称轴133张/方明杰.JPG</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1.005933035034305</v>
+        <v>-1.394652121215965</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01983971220591335</v>
+        <v>-0.2065604445613755</v>
       </c>
       <c r="D19" t="n">
-        <v>0.08078307510973537</v>
+        <v>2.287748098543564</v>
       </c>
       <c r="E19" t="n">
-        <v>0.04683303706954001</v>
+        <v>-4.616678527808899</v>
       </c>
       <c r="F19" t="n">
-        <v>-7.31979672156004</v>
-      </c>
-      <c r="G19" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>41.39924273445749</v>
+        <v>5.528879744159217</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FA0019</t>
+          <t>1.对称轴133张/方渝.JPG</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.8127587858380342</v>
+        <v>-1.52561040361718</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.04782992654461934</v>
+        <v>0.1407390716875503</v>
       </c>
       <c r="D20" t="n">
-        <v>0.03074405470262456</v>
+        <v>1.464867999166433</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.01539437992936601</v>
+        <v>-8.382138574086202</v>
       </c>
       <c r="F20" t="n">
-        <v>22.02643874056162</v>
-      </c>
-      <c r="G20" t="n">
-        <v>69.25</v>
-      </c>
-      <c r="H20" t="n">
-        <v>70.75871636961897</v>
+        <v>-4.292454677367303</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FA0020</t>
+          <t>1.对称轴133张/方策一.JPG</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.802353232483246</v>
+        <v>-2.043948144241262</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.1520557053211865</v>
+        <v>-1.375407750810923</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.01708699170835496</v>
+        <v>-1.008161474825961</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.01320780810503597</v>
+        <v>-9.080995819347681</v>
       </c>
       <c r="F21" t="n">
-        <v>2.272803287593455</v>
-      </c>
-      <c r="G21" t="n">
-        <v>55</v>
-      </c>
-      <c r="H21" t="n">
-        <v>53.47032268160878</v>
+        <v>-4.633583394990856</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FA0021</t>
+          <t>1.对称轴133张/曹强.JPG</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-1.146909801402668</v>
+        <v>0.144899907960269</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.264343247404521</v>
+        <v>1.53206470888034</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2770965373638801</v>
+        <v>-2.204335063247683</v>
       </c>
       <c r="E22" t="n">
-        <v>0.08069877223655295</v>
+        <v>-3.803411205853816</v>
       </c>
       <c r="F22" t="n">
-        <v>6.788711309342019</v>
-      </c>
-      <c r="G22" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>54.75857716207415</v>
+        <v>11.52118506804406</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FA0022</t>
+          <t>1.对称轴133张/曹志颐.JPG</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.01046013462283602</v>
+        <v>-1.1391942673215</v>
       </c>
       <c r="C23" t="n">
-        <v>0.005514654424522049</v>
+        <v>0.6768156799746025</v>
       </c>
       <c r="D23" t="n">
-        <v>0.07631075673910023</v>
+        <v>2.837033522327844</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04258844411476757</v>
+        <v>-2.427922121332433</v>
       </c>
       <c r="F23" t="n">
-        <v>7.025776101435945</v>
-      </c>
-      <c r="G23" t="n">
-        <v>59</v>
-      </c>
-      <c r="H23" t="n">
-        <v>56.73816675800381</v>
+        <v>-3.648829397865244</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FA0023</t>
+          <t>1.对称轴133张/曹歆呓.JPG</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.235197767992575</v>
+        <v>0.131449455019021</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.007090428032473188</v>
+        <v>0.423685130570034</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.08428757974231771</v>
+        <v>-1.911567810011759</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.03974658013697082</v>
+        <v>-7.785638783482317</v>
       </c>
       <c r="F24" t="n">
-        <v>8.126028106200991</v>
-      </c>
-      <c r="G24" t="n">
-        <v>57.75</v>
-      </c>
-      <c r="H24" t="n">
-        <v>57.33722241696333</v>
+        <v>2.944142090354936</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FA0024</t>
+          <t>1.对称轴133张/曹玉兰.JPG</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-1.007739957991068</v>
+        <v>2.483617922646292</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.3537170072661656</v>
+        <v>0.8834410608192557</v>
       </c>
       <c r="D25" t="n">
-        <v>0.05008112318987515</v>
+        <v>1.553717043264696</v>
       </c>
       <c r="E25" t="n">
-        <v>0.01321981745382322</v>
+        <v>-2.058928855419944</v>
       </c>
       <c r="F25" t="n">
-        <v>-13.86252042194556</v>
-      </c>
-      <c r="G25" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="H25" t="n">
-        <v>34.41684022010759</v>
+        <v>-4.03477708886038</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FA0025</t>
+          <t>1.对称轴133张/曾世杰.JPG</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.4398968723311626</v>
+        <v>2.658261303263352</v>
       </c>
       <c r="C26" t="n">
-        <v>0.09503149754846603</v>
+        <v>2.682101253021744</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.007218767585320595</v>
+        <v>3.558588846475617</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.006508124733047401</v>
+        <v>24.34198252777906</v>
       </c>
       <c r="F26" t="n">
-        <v>19.98842580843716</v>
-      </c>
-      <c r="G26" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="H26" t="n">
-        <v>69.20735020800275</v>
+        <v>-5.03219718142332</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FA0026</t>
+          <t>1.对称轴133张/曾众婉.JPG</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.6149746719576873</v>
+        <v>-0.789172843020295</v>
       </c>
       <c r="C27" t="n">
-        <v>0.05329037983791095</v>
+        <v>2.395751924870567</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.009949234315142651</v>
+        <v>-1.603559173200248</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.03231658893284825</v>
+        <v>5.622179257163497</v>
       </c>
       <c r="F27" t="n">
-        <v>9.847437793076784</v>
-      </c>
-      <c r="G27" t="n">
-        <v>58.75</v>
-      </c>
-      <c r="H27" t="n">
-        <v>58.82100434437567</v>
+        <v>5.076037583303045</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FA0027</t>
+          <t>1.对称轴133张/曾佳.JPG</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1894682715792776</v>
+        <v>3.008714375318169</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1563045983916072</v>
+        <v>-0.5510892112237443</v>
       </c>
       <c r="D28" t="n">
-        <v>0.03576631244524728</v>
+        <v>1.354986997064101</v>
       </c>
       <c r="E28" t="n">
-        <v>0.002671200256507592</v>
+        <v>-0.7794895274826699</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5232993596379142</v>
-      </c>
-      <c r="G28" t="n">
-        <v>50</v>
-      </c>
-      <c r="H28" t="n">
-        <v>49.79348066903546</v>
+        <v>-5.889385884559265</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FA0028</t>
+          <t>1.对称轴133张/曾元静.JPG</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.333126693735192</v>
+        <v>0.9686403768813611</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03977842664837054</v>
+        <v>-0.2878103505432567</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.009084111271304164</v>
+        <v>-1.671138807339565</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.005296675197412812</v>
+        <v>5.858417107720417</v>
       </c>
       <c r="F29" t="n">
-        <v>17.39233632382338</v>
-      </c>
-      <c r="G29" t="n">
-        <v>69</v>
-      </c>
-      <c r="H29" t="n">
-        <v>68.32837732440488</v>
+        <v>-11.52353824426907</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FA0029</t>
+          <t>1.对称轴133张/曾夏.JPG</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.062475642832252</v>
+        <v>3.806322114157808</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1934632694758701</v>
+        <v>-0.9027993244524167</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08850338061528897</v>
+        <v>2.937543525494137</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1080699647432044</v>
+        <v>-1.268033128938577</v>
       </c>
       <c r="F30" t="n">
-        <v>24.57799829147792</v>
-      </c>
-      <c r="G30" t="n">
-        <v>76</v>
-      </c>
-      <c r="H30" t="n">
-        <v>77.39188728632486</v>
+        <v>18.32570356285544</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FA0030</t>
+          <t>1.对称轴133张/曾子涵.JPG</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.599922012764404</v>
+        <v>0.6598407001723141</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.08339062225347174</v>
+        <v>0.5237478363803361</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.056905792279691</v>
+        <v>0.3851417092472654</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.02985144669669216</v>
+        <v>8.119741942722317</v>
       </c>
       <c r="F31" t="n">
-        <v>-9.729046483838101</v>
-      </c>
-      <c r="G31" t="n">
-        <v>34</v>
-      </c>
-      <c r="H31" t="n">
-        <v>38.07840030883429</v>
+        <v>-10.40223543940579</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FA0031</t>
+          <t>1.对称轴133张/曾少阳.JPG</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1407770691734715</v>
+        <v>-1.431169871220884</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.09759565441055711</v>
+        <v>1.506631003267747</v>
       </c>
       <c r="D32" t="n">
-        <v>0.05565952110707676</v>
+        <v>-0.4985266070628702</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.02167961123609191</v>
+        <v>-9.677825026560001</v>
       </c>
       <c r="F32" t="n">
-        <v>15.51628331116493</v>
-      </c>
-      <c r="G32" t="n">
-        <v>65</v>
-      </c>
-      <c r="H32" t="n">
-        <v>64.88940716411858</v>
+        <v>-10.30870608264077</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FA0032</t>
+          <t>1.对称轴133张/曾星.JPG</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.09925787530888</v>
+        <v>-1.093789933826658</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0791578830840319</v>
+        <v>1.156357166305098</v>
       </c>
       <c r="D33" t="n">
-        <v>0.157480558639871</v>
+        <v>-1.560055295589956</v>
       </c>
       <c r="E33" t="n">
-        <v>0.03388874014213347</v>
+        <v>-8.569416752823786</v>
       </c>
       <c r="F33" t="n">
-        <v>2.555216717752939</v>
-      </c>
-      <c r="G33" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="H33" t="n">
-        <v>54.5025184415945</v>
+        <v>-7.281858434948072</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FA0033</t>
+          <t>1.对称轴133张/曾朝龙.JPG</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.557098232915792</v>
+        <v>-0.3267073598718884</v>
       </c>
       <c r="C34" t="n">
-        <v>0.002444748103662654</v>
+        <v>-1.800639994896185</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1160598638738367</v>
+        <v>-1.430505619762961</v>
       </c>
       <c r="E34" t="n">
-        <v>0.02556536810972672</v>
+        <v>0.7124440071258624</v>
       </c>
       <c r="F34" t="n">
-        <v>-10.67815781931128</v>
-      </c>
-      <c r="G34" t="n">
-        <v>35.25</v>
-      </c>
-      <c r="H34" t="n">
-        <v>37.2542108667791</v>
+        <v>-4.608354283478205</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FA0034</t>
+          <t>1.对称轴133张/曾楚涵.JPG</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7478050347129247</v>
+        <v>1.763332769127529</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1562995374680489</v>
+        <v>0.9403675616291179</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1010807814333642</v>
+        <v>-1.03033560780565</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.1569893070947237</v>
+        <v>-8.034341778385651</v>
       </c>
       <c r="F35" t="n">
-        <v>25.87002222482648</v>
-      </c>
-      <c r="G35" t="n">
-        <v>73.25</v>
-      </c>
-      <c r="H35" t="n">
-        <v>74.48752579365082</v>
+        <v>2.861380471217926</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FA0035</t>
+          <t>1.对称轴133张/曾献文.JPG</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5.97454536780534</v>
+        <v>-0.1131366878593429</v>
       </c>
       <c r="C36" t="n">
-        <v>0.04590614578745854</v>
+        <v>-1.978682428395789</v>
       </c>
       <c r="D36" t="n">
-        <v>0.03365400107808364</v>
+        <v>-1.337795530367482</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1719651287654151</v>
+        <v>-3.563218458233746</v>
       </c>
       <c r="F36" t="n">
-        <v>-8.220495479630584</v>
-      </c>
-      <c r="G36" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="H36" t="n">
-        <v>47.58309183047238</v>
+        <v>-3.567596812693639</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FA0036</t>
+          <t>1.对称轴133张/曾璐.JPG</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.901531943373943</v>
+        <v>-0.2224350297952407</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1486557842802881</v>
+        <v>-0.4411368119280272</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1652173608084584</v>
+        <v>2.139995921240909</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0137093639198895</v>
+        <v>-7.853934784492893</v>
       </c>
       <c r="F37" t="n">
-        <v>-5.831162349286994</v>
-      </c>
-      <c r="G37" t="n">
-        <v>50</v>
-      </c>
-      <c r="H37" t="n">
-        <v>46.97546876976227</v>
+        <v>6.890414120758516</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FA0037</t>
+          <t>1.对称轴133张/曾铭浩.JPG</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.3151156745513585</v>
+        <v>1.031107045667547</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1579962192041859</v>
+        <v>-3.141105130568697</v>
       </c>
       <c r="D38" t="n">
-        <v>0.07430703423511544</v>
+        <v>-2.359752374653478</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0550421423434836</v>
+        <v>-8.298942921042171</v>
       </c>
       <c r="F38" t="n">
-        <v>-7.349471545792116</v>
-      </c>
-      <c r="G38" t="n">
-        <v>45</v>
-      </c>
-      <c r="H38" t="n">
-        <v>41.88428240369759</v>
+        <v>6.748263463046735</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FA0038</t>
+          <t>1.对称轴133张/曾青云.JPG</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.7199041400813277</v>
+        <v>2.108538083271885</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2132262641596473</v>
+        <v>-0.2381511814496955</v>
       </c>
       <c r="D39" t="n">
-        <v>0.007833041264848906</v>
+        <v>-0.7355983178487057</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1043842482625855</v>
+        <v>-9.139930896074269</v>
       </c>
       <c r="F39" t="n">
-        <v>-10.84461064002791</v>
-      </c>
-      <c r="G39" t="n">
-        <v>39.75</v>
-      </c>
-      <c r="H39" t="n">
-        <v>38.33844544024448</v>
+        <v>-3.974454272115936</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FA0039</t>
+          <t>1.对称轴133张/曾馨琪.JPG</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.558150058655996</v>
+        <v>-1.614511424951756</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1720085732611595</v>
+        <v>0.5681558279048453</v>
       </c>
       <c r="D40" t="n">
-        <v>0.05996800437445211</v>
+        <v>-0.5072073697631028</v>
       </c>
       <c r="E40" t="n">
-        <v>0.02750878061901939</v>
+        <v>-2.984317043460968</v>
       </c>
       <c r="F40" t="n">
-        <v>-7.371833147282227</v>
-      </c>
-      <c r="G40" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="H40" t="n">
-        <v>40.56300167246072</v>
+        <v>-8.575883240612333</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FA0040</t>
+          <t>1.对称轴133张/杜娟.JPG</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.02314338973120209</v>
+        <v>-1.518858410143754</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1208823327971501</v>
+        <v>-0.8886069771135208</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0502742450193425</v>
+        <v>-2.011333731459358</v>
       </c>
       <c r="E41" t="n">
-        <v>0.03203601044692714</v>
+        <v>-7.208035983399456</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.4576283444726075</v>
-      </c>
-      <c r="G41" t="n">
-        <v>47.75</v>
-      </c>
-      <c r="H41" t="n">
-        <v>48.9576243650933</v>
+        <v>9.301405184566027</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FA0041</t>
+          <t>1.对称轴133张/杜晟泽.JPG</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-1.037125394452753</v>
+        <v>-0.2479457006816272</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.1521179130647461</v>
+        <v>-1.849981801595914</v>
       </c>
       <c r="D42" t="n">
-        <v>0.01363992919238915</v>
+        <v>1.083863126683486</v>
       </c>
       <c r="E42" t="n">
-        <v>0.006895498849063467</v>
+        <v>10.73182967811231</v>
       </c>
       <c r="F42" t="n">
-        <v>-7.87196795166249</v>
-      </c>
-      <c r="G42" t="n">
-        <v>40</v>
-      </c>
-      <c r="H42" t="n">
-        <v>40.5368408355281</v>
+        <v>14.11847144659863</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FA0042</t>
+          <t>1.对称轴133张/杜磊.JPG</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5.046606506653323</v>
+        <v>1.048477262183827</v>
       </c>
       <c r="C43" t="n">
-        <v>0.3132444437637302</v>
+        <v>0.5886381331308626</v>
       </c>
       <c r="D43" t="n">
-        <v>0.08192913173994266</v>
+        <v>1.631892215989137</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1224581813383101</v>
+        <v>-4.270984713699197</v>
       </c>
       <c r="F43" t="n">
-        <v>-9.788795964829607</v>
-      </c>
-      <c r="G43" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="H43" t="n">
-        <v>45.35295896533235</v>
+        <v>10.55571385151194</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FA0043</t>
+          <t>1.对称轴133张/查星.JPG</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-1.241161415577777</v>
+        <v>-0.9181576144981186</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.06619726366880363</v>
+        <v>0.4387924580249168</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1162426879479108</v>
+        <v>-0.1310343496329626</v>
       </c>
       <c r="E44" t="n">
-        <v>0.02692140718415944</v>
+        <v>-8.839175961440755</v>
       </c>
       <c r="F44" t="n">
-        <v>-10.95082470504864</v>
-      </c>
-      <c r="G44" t="n">
-        <v>35.25</v>
-      </c>
-      <c r="H44" t="n">
-        <v>37.23001200160768</v>
+        <v>-9.462521116669839</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FA0044</t>
+          <t>1.对称轴133张/樊凤清.JPG</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.7538015949985504</v>
+        <v>-2.516054876402531</v>
       </c>
       <c r="C45" t="n">
-        <v>0.03847977184394904</v>
+        <v>-0.3295770602751216</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1279822721214135</v>
+        <v>-3.266549014675462</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2168403219524676</v>
+        <v>-3.61277089906402</v>
       </c>
       <c r="F45" t="n">
-        <v>11.21852570595351</v>
-      </c>
-      <c r="G45" t="n">
-        <v>62</v>
-      </c>
-      <c r="H45" t="n">
-        <v>60.42554314353946</v>
+        <v>-7.638811400466219</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FA0045</t>
+          <t>1.对称轴133张/樊芷萁.JPG</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-1.296945391670965</v>
+        <v>-0.4754147692083373</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.2714069246309052</v>
+        <v>2.082145270298041</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1051251226135162</v>
+        <v>0.915051766658063</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.08430497695417247</v>
+        <v>7.07690731648422</v>
       </c>
       <c r="F46" t="n">
-        <v>-11.62158892659848</v>
-      </c>
-      <c r="G46" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="H46" t="n">
-        <v>36.19814532419863</v>
+        <v>11.62254716488447</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FA0046</t>
+          <t>1.对称轴133张/段亦宵.JPG</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-1.098608867979076</v>
+        <v>-0.6617333195672509</v>
       </c>
       <c r="C47" t="n">
-        <v>0.04287877121088804</v>
+        <v>-1.831919563711452</v>
       </c>
       <c r="D47" t="n">
-        <v>0.01762187497785925</v>
+        <v>-1.006789401429836</v>
       </c>
       <c r="E47" t="n">
-        <v>0.07344735461358322</v>
+        <v>-1.216845259772811</v>
       </c>
       <c r="F47" t="n">
-        <v>-10.20213889465645</v>
-      </c>
-      <c r="G47" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="H47" t="n">
-        <v>38.41071690483344</v>
+        <v>-4.272309039735364</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FA0047</t>
+          <t>1.对称轴133张/段傲.JPG</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-1.200421348923767</v>
+        <v>-0.7315934152212161</v>
       </c>
       <c r="C48" t="n">
-        <v>0.03398275020773307</v>
+        <v>2.011485122855531</v>
       </c>
       <c r="D48" t="n">
-        <v>0.02791364238392689</v>
+        <v>0.2327599169338874</v>
       </c>
       <c r="E48" t="n">
-        <v>0.04911366913224266</v>
+        <v>-3.684134966964661</v>
       </c>
       <c r="F48" t="n">
-        <v>-7.458616913623649</v>
-      </c>
-      <c r="G48" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="H48" t="n">
-        <v>41.02948846584312</v>
+        <v>5.711886758179749</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FA0048</t>
+          <t>1.对称轴133张/段嘉琪.JPG</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.1397290539462805</v>
+        <v>-1.358716796609967</v>
       </c>
       <c r="C49" t="n">
-        <v>0.09728557167253132</v>
+        <v>-3.191112344333486</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2062876713021312</v>
+        <v>-2.232985519187126</v>
       </c>
       <c r="E49" t="n">
-        <v>0.01860719566618209</v>
+        <v>-5.584588599055658</v>
       </c>
       <c r="F49" t="n">
-        <v>1.044310901566254</v>
-      </c>
-      <c r="G49" t="n">
-        <v>52.75</v>
-      </c>
-      <c r="H49" t="n">
-        <v>50.8042789529275</v>
+        <v>13.66197334163621</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FA0049</t>
+          <t>1.对称轴133张/白中天.JPG</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3.235882414582377</v>
+        <v>0.1924420624455229</v>
       </c>
       <c r="C50" t="n">
-        <v>0.06193541141186617</v>
+        <v>1.13871225815934</v>
       </c>
       <c r="D50" t="n">
-        <v>0.08766046687351049</v>
+        <v>-0.7190264430793984</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.08178085578608353</v>
+        <v>4.620662184774813</v>
       </c>
       <c r="F50" t="n">
-        <v>36.60611691477008</v>
-      </c>
-      <c r="G50" t="n">
-        <v>100</v>
-      </c>
-      <c r="H50" t="n">
-        <v>89.48733101851853</v>
+        <v>15.24761335348299</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FA0050</t>
+          <t>1.对称轴133张/白玛玉珍.JPG</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>5.327347589312514</v>
+        <v>-0.4419399836035535</v>
       </c>
       <c r="C51" t="n">
-        <v>0.2485420809651134</v>
+        <v>3.925551966908467</v>
       </c>
       <c r="D51" t="n">
-        <v>0.01413090148223008</v>
+        <v>1.034111967644479</v>
       </c>
       <c r="E51" t="n">
-        <v>0.116467358162523</v>
+        <v>18.43818258871053</v>
       </c>
       <c r="F51" t="n">
-        <v>-11.01305287298121</v>
-      </c>
-      <c r="G51" t="n">
-        <v>45</v>
-      </c>
-      <c r="H51" t="n">
-        <v>44.27095172360785</v>
+        <v>8.144496876123158</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FA0051</t>
+          <t>1.对称轴133张/白雨.JPG</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.377443336056472</v>
+        <v>-1.633451693541608</v>
       </c>
       <c r="C52" t="n">
-        <v>0.05581597529355761</v>
+        <v>-1.506177666083414</v>
       </c>
       <c r="D52" t="n">
-        <v>0.06202935752966444</v>
+        <v>-1.907519137755633</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0101894815700287</v>
+        <v>-8.561127245715635</v>
       </c>
       <c r="F52" t="n">
-        <v>-4.097723141714814</v>
-      </c>
-      <c r="G52" t="n">
-        <v>48.75</v>
-      </c>
-      <c r="H52" t="n">
-        <v>47.98527167540157</v>
+        <v>-5.690487507786967</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FA0052</t>
+          <t>1.对称轴133张/程丹彤.JPG</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>5.213574956126743</v>
+        <v>2.049941507623809</v>
       </c>
       <c r="C53" t="n">
-        <v>0.003076189478003457</v>
+        <v>4.550729499690828</v>
       </c>
       <c r="D53" t="n">
-        <v>0.08405094754187677</v>
+        <v>0.2834052235853247</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1194234335900573</v>
+        <v>26.75165991246206</v>
       </c>
       <c r="F53" t="n">
-        <v>-9.405161236697586</v>
-      </c>
-      <c r="G53" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="H53" t="n">
-        <v>45.59248095670574</v>
+        <v>8.348000605753933</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FA0053</t>
+          <t>1.对称轴133张/程兮.JPG</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.912302221662099</v>
+        <v>2.267022901123793</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0345172168741997</v>
+        <v>0.1314182553321514</v>
       </c>
       <c r="D54" t="n">
-        <v>0.06876061209677051</v>
+        <v>-0.7897458349658939</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.1554398899568794</v>
+        <v>-8.870643864590196</v>
       </c>
       <c r="F54" t="n">
-        <v>24.4708234244764</v>
-      </c>
-      <c r="G54" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="H54" t="n">
-        <v>76.83944581807087</v>
+        <v>-0.8726480411165535</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FA0054</t>
+          <t>1.对称轴133张/程嘉辉.JPG</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.4242387384579094</v>
+        <v>-0.6131684051137336</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0235773750065242</v>
+        <v>-1.8374103990402</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.08042602416017669</v>
+        <v>1.640491043578442</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.004696506389349965</v>
+        <v>-1.532839068528148</v>
       </c>
       <c r="F55" t="n">
-        <v>-11.02873907874048</v>
-      </c>
-      <c r="G55" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="H55" t="n">
-        <v>38.01583894391218</v>
+        <v>-7.93000308844645</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FA0055</t>
+          <t>1.对称轴133张/程源.JPG</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.242430609060122</v>
+        <v>-0.3777979198946576</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.3725661720678673</v>
+        <v>0.8245745602994129</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.0728629278752706</v>
+        <v>2.935552125073943</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0006932794997791926</v>
+        <v>27.75252709046114</v>
       </c>
       <c r="F56" t="n">
-        <v>-15.5564635263274</v>
-      </c>
-      <c r="G56" t="n">
-        <v>30</v>
-      </c>
-      <c r="H56" t="n">
-        <v>32.33388671083577</v>
+        <v>16.7330475598432</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FA0056</t>
+          <t>1.对称轴133张/程琪语.JPG</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2.702576845503943</v>
+        <v>-0.7174981569056649</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.002885719338573702</v>
+        <v>-0.9877338014859621</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.03836721803582651</v>
+        <v>0.2882978366449759</v>
       </c>
       <c r="E57" t="n">
-        <v>0.003616407131506061</v>
+        <v>9.872123098096781</v>
       </c>
       <c r="F57" t="n">
-        <v>-8.430665517518548</v>
-      </c>
-      <c r="G57" t="n">
-        <v>42</v>
-      </c>
-      <c r="H57" t="n">
-        <v>43.81179146440916</v>
+        <v>2.772714439433102</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FA0057</t>
+          <t>1.对称轴133张/程瑞霖.JPG</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.513198664651331</v>
+        <v>-0.5291057222976931</v>
       </c>
       <c r="C58" t="n">
-        <v>0.04167747626554873</v>
+        <v>2.920062565984284</v>
       </c>
       <c r="D58" t="n">
-        <v>0.01584319652247828</v>
+        <v>-0.5256620999431473</v>
       </c>
       <c r="E58" t="n">
-        <v>0.06218404718976767</v>
+        <v>3.286659161236716</v>
       </c>
       <c r="F58" t="n">
-        <v>-8.233938124104604</v>
-      </c>
-      <c r="G58" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="H58" t="n">
-        <v>39.95008459788851</v>
+        <v>7.060116177469769</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FA0058</t>
+          <t>1.对称轴133张/范琳玉.JPG</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.381879018487982</v>
+        <v>1.436379325322958</v>
       </c>
       <c r="C59" t="n">
-        <v>0.01171620543944596</v>
+        <v>-0.6831500481715347</v>
       </c>
       <c r="D59" t="n">
-        <v>0.03771633514988932</v>
+        <v>-1.837341861166544</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.0575154445686132</v>
+        <v>-7.090097133156296</v>
       </c>
       <c r="F59" t="n">
-        <v>-11.0270095245644</v>
-      </c>
-      <c r="G59" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="H59" t="n">
-        <v>37.16054521963498</v>
+        <v>1.36627979962136</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FA0059</t>
+          <t>1.对称轴133张/范皖皖.JPG</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.461715725824299</v>
+        <v>-0.06470290929586202</v>
       </c>
       <c r="C60" t="n">
-        <v>0.1161182697678644</v>
+        <v>-1.838591180849062</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.08760221624504944</v>
+        <v>2.800939007482737</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.0543655053026323</v>
+        <v>-4.088579495787936</v>
       </c>
       <c r="F60" t="n">
-        <v>-10.71485042893917</v>
-      </c>
-      <c r="G60" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H60" t="n">
-        <v>37.37510106012336</v>
+        <v>10.47217132756675</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FA0060</t>
+          <t>1.对称轴133张/董何鑫.JPG</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.498273020884683</v>
+        <v>-1.858586181155417</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.07079369581166342</v>
+        <v>-2.981575027335126</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.07210390073185194</v>
+        <v>-2.053654705372836</v>
       </c>
       <c r="E61" t="n">
-        <v>0.02564962926985969</v>
+        <v>-1.759238544839354</v>
       </c>
       <c r="F61" t="n">
-        <v>-7.760877889423692</v>
-      </c>
-      <c r="G61" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="H61" t="n">
-        <v>40.2011177890846</v>
+        <v>3.952624541152677</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FA0061</t>
+          <t>1.对称轴133张/董芮君.JPG</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.4254171694483647</v>
+        <v>-0.5966523392972535</v>
       </c>
       <c r="C62" t="n">
-        <v>0.4841349806802632</v>
+        <v>-1.46233315073213</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.01475120503332591</v>
+        <v>1.11156162314242</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.09650938018371229</v>
+        <v>-7.957790905161528</v>
       </c>
       <c r="F62" t="n">
-        <v>-15.40472042576984</v>
-      </c>
-      <c r="G62" t="n">
-        <v>36</v>
-      </c>
-      <c r="H62" t="n">
-        <v>34.12025346691169</v>
+        <v>-3.948548478834828</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FA0062</t>
+          <t>1.对称轴133张/董英涵.JPG</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.4068239778373091</v>
+        <v>-0.9150911022804941</v>
       </c>
       <c r="C63" t="n">
-        <v>0.2303587176321008</v>
+        <v>-0.2301754670141016</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0570407372730919</v>
+        <v>2.680632854292611</v>
       </c>
       <c r="E63" t="n">
-        <v>0.1084760825570328</v>
+        <v>15.70728495182198</v>
       </c>
       <c r="F63" t="n">
-        <v>-11.59149385375846</v>
-      </c>
-      <c r="G63" t="n">
-        <v>39</v>
-      </c>
-      <c r="H63" t="n">
-        <v>37.97507437253311</v>
+        <v>16.81025217896339</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FA0063</t>
+          <t>1.对称轴133张/蔡修杰.JPG</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.3059751365474495</v>
+        <v>0.1752709077492166</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.01780970371178184</v>
+        <v>-0.1467767474689791</v>
       </c>
       <c r="D64" t="n">
-        <v>0.003512761970848248</v>
+        <v>-0.6130770028321979</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.004778856287897423</v>
+        <v>-8.631925772822651</v>
       </c>
       <c r="F64" t="n">
-        <v>-16.25810466434841</v>
-      </c>
-      <c r="G64" t="n">
-        <v>31</v>
-      </c>
-      <c r="H64" t="n">
-        <v>32.99436106774198</v>
+        <v>0.5144120311579038</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FA0064</t>
+          <t>1.对称轴133张/蔡艳红.JPG</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-1.589606816098626</v>
+        <v>-0.2477839142854072</v>
       </c>
       <c r="C65" t="n">
-        <v>0.1193275248183695</v>
+        <v>-1.85459075480455</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.005823466090028811</v>
+        <v>-1.083233021362285</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.03628204468012456</v>
+        <v>11.47002222131326</v>
       </c>
       <c r="F65" t="n">
-        <v>-11.38203000041301</v>
-      </c>
-      <c r="G65" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H65" t="n">
-        <v>36.68310186420323</v>
+        <v>8.856822218255733</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FA0065</t>
+          <t>1.对称轴133张/蔡芊.JPG</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.139814538927842</v>
+        <v>-0.66364274218371</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1900671553731277</v>
+        <v>-0.3162068186284575</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.3561634848113187</v>
+        <v>1.638452830450653</v>
       </c>
       <c r="E66" t="n">
-        <v>0.05035243149002503</v>
+        <v>-3.665116061382426</v>
       </c>
       <c r="F66" t="n">
-        <v>-6.410573067433655</v>
-      </c>
-      <c r="G66" t="n">
-        <v>40.75</v>
-      </c>
-      <c r="H66" t="n">
-        <v>41.53125085161073</v>
+        <v>5.323582874193835</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FA0066</t>
+          <t>1.对称轴133张/蔡芸阳.JPG</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.8465383988327484</v>
+        <v>-0.7192295848182336</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.0189305070673425</v>
+        <v>-0.5683955395310749</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.07442943510382433</v>
+        <v>1.259611826093948</v>
       </c>
       <c r="E67" t="n">
-        <v>0.01469916454017561</v>
+        <v>-8.064059260819803</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.980891093485432</v>
-      </c>
-      <c r="G67" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="H67" t="n">
-        <v>47.67142639671754</v>
+        <v>-4.622524025141511</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FA0067</t>
+          <t>1.对称轴133张/邓乔月.JPG</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>6.436141012670483</v>
+        <v>-0.8624667706845747</v>
       </c>
       <c r="C68" t="n">
-        <v>0.3109238380380968</v>
+        <v>-1.896784176002457</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.02129313526383948</v>
+        <v>-3.540058927258662</v>
       </c>
       <c r="E68" t="n">
-        <v>0.1677883408154581</v>
+        <v>4.791729180261657</v>
       </c>
       <c r="F68" t="n">
-        <v>-9.490279660958061</v>
-      </c>
-      <c r="G68" t="n">
-        <v>53</v>
-      </c>
-      <c r="H68" t="n">
-        <v>46.98079706196877</v>
+        <v>-9.132849223866133</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FA0068</t>
+          <t>1.对称轴133张/邓力恒.JPG</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.116718825262653</v>
+        <v>-0.578918297010362</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.004820312150677341</v>
+        <v>-1.623884081851177</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.01086955700699958</v>
+        <v>1.558301237737808</v>
       </c>
       <c r="E69" t="n">
-        <v>0.04990982107346274</v>
+        <v>-2.718032883723045</v>
       </c>
       <c r="F69" t="n">
-        <v>2.025042440887321</v>
-      </c>
-      <c r="G69" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="H69" t="n">
-        <v>50.52006023420713</v>
+        <v>11.50627077396329</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FA0069</t>
+          <t>1.对称轴133张/邓墨苒.JPG</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.286042022536349</v>
+        <v>0.5593017150252559</v>
       </c>
       <c r="C70" t="n">
-        <v>0.1112991852426402</v>
+        <v>1.704666439813528</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.008621881736105759</v>
+        <v>2.804730972182119</v>
       </c>
       <c r="E70" t="n">
-        <v>0.04037025759244305</v>
+        <v>11.50508572522984</v>
       </c>
       <c r="F70" t="n">
-        <v>-10.88835976778936</v>
-      </c>
-      <c r="G70" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H70" t="n">
-        <v>37.5461624374399</v>
+        <v>2.394951896865855</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FA0070</t>
+          <t>1.对称轴133张/邓必红.JPG</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.039528551938321</v>
+        <v>0.7237751098084636</v>
       </c>
       <c r="C71" t="n">
-        <v>0.02238877938015919</v>
+        <v>-2.254801819486103</v>
       </c>
       <c r="D71" t="n">
-        <v>0.08173145704725064</v>
+        <v>-0.3230077258550696</v>
       </c>
       <c r="E71" t="n">
-        <v>0.08549559175435918</v>
+        <v>-4.607068507703037</v>
       </c>
       <c r="F71" t="n">
-        <v>-8.467204877288035</v>
-      </c>
-      <c r="G71" t="n">
-        <v>41.75</v>
-      </c>
-      <c r="H71" t="n">
-        <v>40.26039906562205</v>
+        <v>10.96733969235228</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FA0071</t>
+          <t>1.对称轴133张/邓悦兴.JPG</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.091536162494423</v>
+        <v>1.903108399653423</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.1008968161720675</v>
+        <v>-1.723611741177438</v>
       </c>
       <c r="D72" t="n">
-        <v>0.03412448045604125</v>
+        <v>1.593433170622749</v>
       </c>
       <c r="E72" t="n">
-        <v>0.02773614549217657</v>
+        <v>-2.304303177144381</v>
       </c>
       <c r="F72" t="n">
-        <v>16.27092371338102</v>
-      </c>
-      <c r="G72" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="H72" t="n">
-        <v>64.71786802732947</v>
+        <v>-4.954889902837764</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FA0072</t>
+          <t>1.对称轴133张/邓文慧.JPG</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.3875365836969932</v>
+        <v>-0.9197628690395833</v>
       </c>
       <c r="C73" t="n">
-        <v>0.012629730764257</v>
+        <v>-1.136102820270565</v>
       </c>
       <c r="D73" t="n">
-        <v>0.05763294360347487</v>
+        <v>2.761093783985367</v>
       </c>
       <c r="E73" t="n">
-        <v>0.02876412883358177</v>
+        <v>-9.603936771886953</v>
       </c>
       <c r="F73" t="n">
-        <v>-7.669017591038402</v>
-      </c>
-      <c r="G73" t="n">
-        <v>43.75</v>
-      </c>
-      <c r="H73" t="n">
-        <v>41.61998929513256</v>
+        <v>-4.631721240338291</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FA0073</t>
+          <t>1.对称轴133张/邓洋洋.JPG</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.494727599699329</v>
+        <v>1.565667158262312</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.1816882028165158</v>
+        <v>-0.7391124920515606</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.1516877844445743</v>
+        <v>1.525554712546145</v>
       </c>
       <c r="E74" t="n">
-        <v>0.04201431609739534</v>
+        <v>-3.105824969479564</v>
       </c>
       <c r="F74" t="n">
-        <v>-6.155987588954174</v>
-      </c>
-      <c r="G74" t="n">
-        <v>39.75</v>
-      </c>
-      <c r="H74" t="n">
-        <v>41.63543980684943</v>
+        <v>-6.687547660160705</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FA0074</t>
+          <t>1.对称轴133张/邓雨宸.JPG</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.159557383373757</v>
+        <v>-1.435555250748394</v>
       </c>
       <c r="C75" t="n">
-        <v>0.03190430647077595</v>
+        <v>-2.440689775639644</v>
       </c>
       <c r="D75" t="n">
-        <v>0.02026867988358471</v>
+        <v>-2.106955999322252</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.002500179778190479</v>
+        <v>-9.031643239395455</v>
       </c>
       <c r="F75" t="n">
-        <v>0.2763081967475018</v>
-      </c>
-      <c r="G75" t="n">
-        <v>48</v>
-      </c>
-      <c r="H75" t="n">
-        <v>48.74394028661661</v>
+        <v>-4.064752319110989</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FA0075</t>
+          <t>1.对称轴133张/邓雪.JPG</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.1069637387814656</v>
+        <v>1.173394393282677</v>
       </c>
       <c r="C76" t="n">
-        <v>0.489802492970533</v>
+        <v>-0.2695091282995346</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.07859435949896071</v>
+        <v>-0.7238467948686048</v>
       </c>
       <c r="E76" t="n">
-        <v>0.1560763662989282</v>
+        <v>-0.9452014924183515</v>
       </c>
       <c r="F76" t="n">
-        <v>-15.01685493430767</v>
-      </c>
-      <c r="G76" t="n">
-        <v>35.75</v>
-      </c>
-      <c r="H76" t="n">
-        <v>35.23490997091094</v>
+        <v>-7.652766895246138</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FA0076</t>
+          <t>1.对称轴133张/都涵睿.JPG</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.09508182458497895</v>
+        <v>-0.8816548956775931</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.02260317339233502</v>
+        <v>-0.4309925643573693</v>
       </c>
       <c r="D77" t="n">
-        <v>0.03521710139730028</v>
+        <v>-2.975055218318225</v>
       </c>
       <c r="E77" t="n">
-        <v>0.03784176102006499</v>
+        <v>6.171250063643639</v>
       </c>
       <c r="F77" t="n">
-        <v>15.43772893459915</v>
-      </c>
-      <c r="G77" t="n">
-        <v>65</v>
-      </c>
-      <c r="H77" t="n">
-        <v>64.97061946570587</v>
+        <v>2.832689363826001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FA0077</t>
+          <t>1.对称轴133张/阿依晓芳.JPG</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.8918589681081895</v>
+        <v>0.3127813999182748</v>
       </c>
       <c r="C78" t="n">
-        <v>0.08399310590060786</v>
+        <v>-0.05753789858607272</v>
       </c>
       <c r="D78" t="n">
-        <v>0.002022585189018733</v>
+        <v>1.56302690859048</v>
       </c>
       <c r="E78" t="n">
-        <v>0.08035505720233339</v>
+        <v>15.4195413168848</v>
       </c>
       <c r="F78" t="n">
-        <v>18.68115434754743</v>
-      </c>
-      <c r="G78" t="n">
-        <v>66</v>
-      </c>
-      <c r="H78" t="n">
-        <v>67.53318279439783</v>
+        <v>6.487591688975696</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FA0078</t>
+          <t>1.对称轴133张/陈丽.JPG</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.8449328459231165</v>
+        <v>-0.6222545213794402</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.02877271443479801</v>
+        <v>0.7844826031774874</v>
       </c>
       <c r="D79" t="n">
-        <v>0.1472042073607978</v>
+        <v>2.671165332785345</v>
       </c>
       <c r="E79" t="n">
-        <v>0.04290662632141246</v>
+        <v>15.86181135903991</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.050299217229937</v>
-      </c>
-      <c r="G79" t="n">
-        <v>47</v>
-      </c>
-      <c r="H79" t="n">
-        <v>47.84362272276106</v>
+        <v>12.63019864216004</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FA0079</t>
+          <t>1.对称轴133张/陈伟.JPG</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.9639865310881729</v>
+        <v>0.5034672415723578</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.1785227779490856</v>
+        <v>-1.327960142354446</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.4026329998048712</v>
+        <v>-1.696308170713517</v>
       </c>
       <c r="E80" t="n">
-        <v>0.0433240551048223</v>
+        <v>9.411026074211717</v>
       </c>
       <c r="F80" t="n">
-        <v>-4.140812021436464</v>
-      </c>
-      <c r="G80" t="n">
-        <v>43</v>
-      </c>
-      <c r="H80" t="n">
-        <v>43.9348863914929</v>
+        <v>12.44434507973398</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FA0080</t>
+          <t>1.对称轴133张/陈佳倩.JPG</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-1.504328516769053</v>
+        <v>-1.164955981790282</v>
       </c>
       <c r="C81" t="n">
-        <v>0.06082921274835142</v>
+        <v>-3.607112829050522</v>
       </c>
       <c r="D81" t="n">
-        <v>0.007815403315127355</v>
+        <v>-1.381394430446108</v>
       </c>
       <c r="E81" t="n">
-        <v>0.01056759115167465</v>
+        <v>-4.91802824020469</v>
       </c>
       <c r="F81" t="n">
-        <v>-8.530414633980664</v>
-      </c>
-      <c r="G81" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="H81" t="n">
-        <v>39.62198572313208</v>
+        <v>6.291894897275045</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FA0081</t>
+          <t>1.对称轴133张/陈俊.JPG</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1.078537254317792</v>
+        <v>-0.09117632145964703</v>
       </c>
       <c r="C82" t="n">
-        <v>0.09571835812107893</v>
+        <v>0.3642356065668059</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.1569834777118474</v>
+        <v>-1.541764011933154</v>
       </c>
       <c r="E82" t="n">
-        <v>0.06583696260325263</v>
+        <v>-7.590695735533426</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.6646705802841336</v>
-      </c>
-      <c r="G82" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="H82" t="n">
-        <v>49.99595518371283</v>
+        <v>-7.172696121857135</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FA0082</t>
+          <t>1.对称轴133张/陈兴烨.JPG</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-1.664748920490952</v>
+        <v>0.3170458415439674</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.3888873765605262</v>
+        <v>0.3288692066273025</v>
       </c>
       <c r="D83" t="n">
-        <v>0.02892495216947109</v>
+        <v>0.07053373586566253</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.1503747399759636</v>
+        <v>-7.436099830486964</v>
       </c>
       <c r="F83" t="n">
-        <v>-16.70239934662223</v>
-      </c>
-      <c r="G83" t="n">
-        <v>26</v>
-      </c>
-      <c r="H83" t="n">
-        <v>30.70003123518645</v>
+        <v>0.7108877955666724</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FA0083</t>
+          <t>1.对称轴133张/陈冠宇.JPG</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1.718839210076555</v>
+        <v>-1.066707364704562</v>
       </c>
       <c r="C84" t="n">
-        <v>0.1679749903857483</v>
+        <v>-2.455310891727084</v>
       </c>
       <c r="D84" t="n">
-        <v>0.01540296086051579</v>
+        <v>-1.94825797275524</v>
       </c>
       <c r="E84" t="n">
-        <v>0.01277363728108944</v>
+        <v>-9.02622228187523</v>
       </c>
       <c r="F84" t="n">
-        <v>-7.691602961724481</v>
-      </c>
-      <c r="G84" t="n">
-        <v>45.25</v>
-      </c>
-      <c r="H84" t="n">
-        <v>43.80090450354606</v>
+        <v>-6.149764739821228</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FA0084</t>
+          <t>1.对称轴133张/陈发扬.JPG</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-1.156839737563298</v>
+        <v>-0.8862059257029768</v>
       </c>
       <c r="C85" t="n">
-        <v>0.02500611690278876</v>
+        <v>1.170143122898532</v>
       </c>
       <c r="D85" t="n">
-        <v>0.01760080292337083</v>
+        <v>1.506970367349401</v>
       </c>
       <c r="E85" t="n">
-        <v>0.03131271897157493</v>
+        <v>7.260197707129278</v>
       </c>
       <c r="F85" t="n">
-        <v>-16.23584146880923</v>
-      </c>
-      <c r="G85" t="n">
-        <v>30</v>
-      </c>
-      <c r="H85" t="n">
-        <v>32.25875509909188</v>
+        <v>-8.936535189224278</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FA0085</t>
+          <t>1.对称轴133张/陈嘉伟.JPG</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-1.692215654188905</v>
+        <v>-1.615214788737123</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.4051449586324293</v>
+        <v>-0.6403352908803337</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.007636684970934529</v>
+        <v>-1.616668992800106</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.1490136856329301</v>
+        <v>-3.197091886858789</v>
       </c>
       <c r="F86" t="n">
-        <v>-16.15241189988916</v>
-      </c>
-      <c r="G86" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="H86" t="n">
-        <v>31.17109378335229</v>
+        <v>-0.9352856249403783</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FA0086</t>
+          <t>1.对称轴133张/陈垚舟.JPG</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2.246149512871591</v>
+        <v>-1.30939737847137</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.07830952871016465</v>
+        <v>-0.5994403206191773</v>
       </c>
       <c r="D87" t="n">
-        <v>0.2161500095022202</v>
+        <v>-2.138597341578059</v>
       </c>
       <c r="E87" t="n">
-        <v>0.003746212632428188</v>
+        <v>-5.161066129364396</v>
       </c>
       <c r="F87" t="n">
-        <v>0.5765613914020628</v>
-      </c>
-      <c r="G87" t="n">
-        <v>53</v>
-      </c>
-      <c r="H87" t="n">
-        <v>52.5418142643648</v>
+        <v>-0.6852620808503211</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FA0087</t>
+          <t>1.对称轴133张/陈娟.JPG</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-0.08100311311841665</v>
+        <v>-0.6079934006710385</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.08270409458473751</v>
+        <v>-2.555387334669687</v>
       </c>
       <c r="D88" t="n">
-        <v>0.2100683634977101</v>
+        <v>-0.4098382990564001</v>
       </c>
       <c r="E88" t="n">
-        <v>0.06372184715044077</v>
+        <v>4.977871027986643</v>
       </c>
       <c r="F88" t="n">
-        <v>1.648613138064015</v>
-      </c>
-      <c r="G88" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="H88" t="n">
-        <v>51.33621280767569</v>
+        <v>-0.02841524447290674</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FA0088</t>
+          <t>1.对称轴133张/陈婕.JPG</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-1.120776279612269</v>
+        <v>-1.280669212992616</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.1591366265524895</v>
+        <v>-2.110028266341414</v>
       </c>
       <c r="D89" t="n">
-        <v>0.04662688057935624</v>
+        <v>-1.220195742418374</v>
       </c>
       <c r="E89" t="n">
-        <v>0.01684647441102353</v>
+        <v>18.5157113395711</v>
       </c>
       <c r="F89" t="n">
-        <v>0.4833739485413225</v>
-      </c>
-      <c r="G89" t="n">
-        <v>47</v>
-      </c>
-      <c r="H89" t="n">
-        <v>48.84445106403363</v>
+        <v>7.581418631297878</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FA0089</t>
+          <t>1.对称轴133张/陈婷.JPG</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-1.388233002146266</v>
+        <v>-1.482707242388506</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.1628481157890292</v>
+        <v>-0.9559477290455789</v>
       </c>
       <c r="D90" t="n">
-        <v>0.01571318046174382</v>
+        <v>0.3113302716706743</v>
       </c>
       <c r="E90" t="n">
-        <v>0.03049333980212027</v>
+        <v>13.50955299951793</v>
       </c>
       <c r="F90" t="n">
-        <v>-7.416746741913114</v>
-      </c>
-      <c r="G90" t="n">
-        <v>40</v>
-      </c>
-      <c r="H90" t="n">
-        <v>40.65589532708209</v>
+        <v>-0.2943248839711138</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FA0090</t>
+          <t>1.对称轴133张/陈嫣然.JPG</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-1.007447099680856</v>
+        <v>-0.7746483463704289</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.179610176635413</v>
+        <v>5.996755685540788</v>
       </c>
       <c r="D91" t="n">
-        <v>0.0521635514558712</v>
+        <v>-1.678228664365112</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.1314500381868239</v>
+        <v>-3.802035150272426</v>
       </c>
       <c r="F91" t="n">
-        <v>26.02703840590439</v>
-      </c>
-      <c r="G91" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="H91" t="n">
-        <v>74.33821130952384</v>
+        <v>22.41855989125028</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FA0091</t>
+          <t>1.对称轴133张/陈子墨.JPG</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-1.436339877784576</v>
+        <v>-0.4702046324210806</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.03982098472476731</v>
+        <v>-2.983670772996459</v>
       </c>
       <c r="D92" t="n">
-        <v>0.04065017229371211</v>
+        <v>-2.375454921406944</v>
       </c>
       <c r="E92" t="n">
-        <v>0.03885586212447938</v>
+        <v>-5.454492972398293</v>
       </c>
       <c r="F92" t="n">
-        <v>-8.483671694665851</v>
-      </c>
-      <c r="G92" t="n">
-        <v>37.75</v>
-      </c>
-      <c r="H92" t="n">
-        <v>39.69719014390962</v>
+        <v>7.051726715006101</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FA0092</t>
+          <t>1.对称轴133张/陈子攸.JPG</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.212794924625194</v>
+        <v>-0.6015419883159538</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.1595554419656391</v>
+        <v>-0.4354660176430283</v>
       </c>
       <c r="D93" t="n">
-        <v>0.2183376589222729</v>
+        <v>-0.5650314699434664</v>
       </c>
       <c r="E93" t="n">
-        <v>0.02318550087737606</v>
+        <v>5.56288989062961</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.8163137126971198</v>
-      </c>
-      <c r="G93" t="n">
-        <v>49.75</v>
-      </c>
-      <c r="H93" t="n">
-        <v>49.05596559642876</v>
+        <v>-10.26128033227726</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FA0093</t>
+          <t>1.对称轴133张/陈宇佳.JPG</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-1.228610271149877</v>
+        <v>0.997671549645921</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.07624923044967737</v>
+        <v>-0.9767913484767358</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.1601458511467354</v>
+        <v>2.81946088956897</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.09264468791173358</v>
+        <v>15.97890408553839</v>
       </c>
       <c r="F94" t="n">
-        <v>11.46962760661058</v>
-      </c>
-      <c r="G94" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="H94" t="n">
-        <v>59.48949423261926</v>
+        <v>2.521991572840026</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FA0094</t>
+          <t>1.对称轴133张/陈宇凡.JPG</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-1.345461254697558</v>
+        <v>0.161512334625265</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.3349448386098853</v>
+        <v>-0.545250922961667</v>
       </c>
       <c r="D95" t="n">
-        <v>0.006846977888471285</v>
+        <v>0.3132984957721832</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.09241840378197429</v>
+        <v>-11.95300139171661</v>
       </c>
       <c r="F95" t="n">
-        <v>-13.02912335372045</v>
-      </c>
-      <c r="G95" t="n">
-        <v>32</v>
-      </c>
-      <c r="H95" t="n">
-        <v>34.78241579374529</v>
+        <v>-14.51532176660227</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FA0095</t>
+          <t>1.对称轴133张/陈宇博.JPG</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.03895477756686121</v>
+        <v>0.2835186004296949</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.05766419084655494</v>
+        <v>-0.8768098116497776</v>
       </c>
       <c r="D96" t="n">
-        <v>0.009398861885083818</v>
+        <v>3.016877715932547</v>
       </c>
       <c r="E96" t="n">
-        <v>0.07603520988876393</v>
+        <v>28.93948168006648</v>
       </c>
       <c r="F96" t="n">
-        <v>-8.516688935516333</v>
-      </c>
-      <c r="G96" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="H96" t="n">
-        <v>41.12755238964445</v>
+        <v>16.95316856433741</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FA0096</t>
+          <t>1.对称轴133张/陈安静.JPG</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-1.056266725802585</v>
+        <v>-0.01372053888615611</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.04684428864031974</v>
+        <v>-0.9831879882710692</v>
       </c>
       <c r="D97" t="n">
-        <v>0.1179354977974864</v>
+        <v>1.656787142394667</v>
       </c>
       <c r="E97" t="n">
-        <v>0.2250341745402091</v>
+        <v>-7.551817887422085</v>
       </c>
       <c r="F97" t="n">
-        <v>10.58415492215259</v>
-      </c>
-      <c r="G97" t="n">
-        <v>58.25</v>
-      </c>
-      <c r="H97" t="n">
-        <v>59.40153024671407</v>
+        <v>1.116509354634538</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FA0097</t>
+          <t>1.对称轴133张/陈小洪.JPG</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-1.19939175204457</v>
+        <v>1.945195996254762</v>
       </c>
       <c r="C98" t="n">
-        <v>0.1728503076023108</v>
+        <v>1.317834611847362</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.01719222254030735</v>
+        <v>3.551187437700941</v>
       </c>
       <c r="E98" t="n">
-        <v>0.05473773696166516</v>
+        <v>14.51486019698722</v>
       </c>
       <c r="F98" t="n">
-        <v>-6.62757467343762</v>
-      </c>
-      <c r="G98" t="n">
-        <v>44.25</v>
-      </c>
-      <c r="H98" t="n">
-        <v>41.96094606320812</v>
+        <v>3.552991839659558</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FA0098</t>
+          <t>1.对称轴133张/陈尧.JPG</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-1.075371402059823</v>
+        <v>-0.9704668492566177</v>
       </c>
       <c r="C99" t="n">
-        <v>0.04464165093659871</v>
+        <v>0.6196569709298263</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.2869659460970592</v>
+        <v>-1.132383680679895</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.0519144985206603</v>
+        <v>-8.521201516886808</v>
       </c>
       <c r="F99" t="n">
-        <v>3.561537753434116</v>
-      </c>
-      <c r="G99" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="H99" t="n">
-        <v>51.76944422435984</v>
+        <v>-4.228534841656526</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FA0099</t>
+          <t>1.对称轴133张/陈庆敏.JPG</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-0.5810897702066328</v>
+        <v>-1.181073839721909</v>
       </c>
       <c r="C100" t="n">
-        <v>0.2116167591829445</v>
+        <v>0.1525886931753729</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.02069391531580453</v>
+        <v>0.5585135076826203</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.01243020200894834</v>
+        <v>-3.396082133948342</v>
       </c>
       <c r="F100" t="n">
-        <v>-8.153199459387469</v>
-      </c>
-      <c r="G100" t="n">
-        <v>43</v>
-      </c>
-      <c r="H100" t="n">
-        <v>41.02172007893072</v>
+        <v>-11.19770947807116</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FA0100</t>
+          <t>1.对称轴133张/陈志飞.JPG</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-0.4294916396611081</v>
+        <v>1.930765958523512</v>
       </c>
       <c r="C101" t="n">
-        <v>0.3230470211515646</v>
+        <v>-1.459795907527762</v>
       </c>
       <c r="D101" t="n">
-        <v>0.03209251619979888</v>
+        <v>1.483173875317418</v>
       </c>
       <c r="E101" t="n">
-        <v>0.1221118430373578</v>
+        <v>13.74474733982223</v>
       </c>
       <c r="F101" t="n">
-        <v>-13.61868321493523</v>
-      </c>
-      <c r="G101" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H101" t="n">
-        <v>36.00659319245904</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>MeanAbsSHAP</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Normalized_Weight</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Eyebrow</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1.331536712723312</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.1093197169739933</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Eye</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.1301912707850539</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.01068875738739325</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Nose</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.07798948907827585</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.006402969434876622</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Mouth</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.06621897117723489</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.00543660502803469</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Facial Contour</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>10.5742699232182</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.8681519511757021</v>
+        <v>-10.20098785035214</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈思.JPG</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>-0.02337821600266518</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-0.9035596869574192</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1.120339616441855</v>
+      </c>
+      <c r="E102" t="n">
+        <v>-9.74034222532336</v>
+      </c>
+      <c r="F102" t="n">
+        <v>-9.872656072375044</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈思源.JPG</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>-0.5765351718045859</v>
+      </c>
+      <c r="C103" t="n">
+        <v>1.363530286591957</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.2351176884761856</v>
+      </c>
+      <c r="E103" t="n">
+        <v>8.531075717273849</v>
+      </c>
+      <c r="F103" t="n">
+        <v>18.38388156191258</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈怡洁.JPG</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>2.395102439083818</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1.080786648824938</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1.548130079714595</v>
+      </c>
+      <c r="E104" t="n">
+        <v>8.802208550998028</v>
+      </c>
+      <c r="F104" t="n">
+        <v>-10.41749096950487</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈悦.JPG</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>0.7898937299155472</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-2.335542035307578</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1.104961270443811</v>
+      </c>
+      <c r="E105" t="n">
+        <v>-10.24974443081492</v>
+      </c>
+      <c r="F105" t="n">
+        <v>-7.834165118453504</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈惠.JPG</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>-0.4426584060953301</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-1.700337144334398</v>
+      </c>
+      <c r="D106" t="n">
+        <v>2.409986062599069</v>
+      </c>
+      <c r="E106" t="n">
+        <v>-8.572937645892488</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.578850549506464</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈意婕.JPG</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>-0.5323648985998762</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0.3279338849737366</v>
+      </c>
+      <c r="D107" t="n">
+        <v>2.297436358143992</v>
+      </c>
+      <c r="E107" t="n">
+        <v>11.2237049921556</v>
+      </c>
+      <c r="F107" t="n">
+        <v>17.78202641244317</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈曹瑞.JPG</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>-0.3066893704507445</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0.4681321478543409</v>
+      </c>
+      <c r="D108" t="n">
+        <v>-1.897141140654506</v>
+      </c>
+      <c r="E108" t="n">
+        <v>-2.270625602225249</v>
+      </c>
+      <c r="F108" t="n">
+        <v>-10.81910595207388</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈有谋.JPG</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>-1.018134544709404</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-2.17451203337605</v>
+      </c>
+      <c r="D109" t="n">
+        <v>-0.7288372765203657</v>
+      </c>
+      <c r="E109" t="n">
+        <v>-11.25177982488318</v>
+      </c>
+      <c r="F109" t="n">
+        <v>-13.40716623806113</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈朴阳.JPG</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1.206153944999595</v>
+      </c>
+      <c r="C110" t="n">
+        <v>6.455043483012694</v>
+      </c>
+      <c r="D110" t="n">
+        <v>-1.341562541220564</v>
+      </c>
+      <c r="E110" t="n">
+        <v>-5.555062815168094</v>
+      </c>
+      <c r="F110" t="n">
+        <v>15.74916467749281</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈李睿.JPG</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>-0.6219800819722155</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0.6778072440966498</v>
+      </c>
+      <c r="D111" t="n">
+        <v>-2.193736497160054</v>
+      </c>
+      <c r="E111" t="n">
+        <v>-3.989116311367684</v>
+      </c>
+      <c r="F111" t="n">
+        <v>12.93242906218652</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈杰.JPG</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>-0.6293070425050444</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-2.144054858295816</v>
+      </c>
+      <c r="D112" t="n">
+        <v>-1.514551423619208</v>
+      </c>
+      <c r="E112" t="n">
+        <v>-3.54744771593398</v>
+      </c>
+      <c r="F112" t="n">
+        <v>4.409931122803979</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈松毅.JPG</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>2.200220781024497</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1.939045250836437</v>
+      </c>
+      <c r="D113" t="n">
+        <v>-2.342229478969167</v>
+      </c>
+      <c r="E113" t="n">
+        <v>17.57615714814933</v>
+      </c>
+      <c r="F113" t="n">
+        <v>2.133876381408846</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈梦雪.JPG</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>-1.219973046227205</v>
+      </c>
+      <c r="C114" t="n">
+        <v>1.47422709418484</v>
+      </c>
+      <c r="D114" t="n">
+        <v>-0.2207408283482724</v>
+      </c>
+      <c r="E114" t="n">
+        <v>20.13486655741868</v>
+      </c>
+      <c r="F114" t="n">
+        <v>-0.1821430279114251</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈欣妍.JPG</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>0.4487308390589813</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.6005922361554028</v>
+      </c>
+      <c r="D115" t="n">
+        <v>-0.02368120740018852</v>
+      </c>
+      <c r="E115" t="n">
+        <v>-8.199504150779259</v>
+      </c>
+      <c r="F115" t="n">
+        <v>-6.459067634584967</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈治宇.JPG</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>-0.506624106700006</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0.7646035428414445</v>
+      </c>
+      <c r="D116" t="n">
+        <v>-0.9146847720761088</v>
+      </c>
+      <c r="E116" t="n">
+        <v>-2.518705968319611</v>
+      </c>
+      <c r="F116" t="n">
+        <v>-5.701685279962346</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈泊桥.JPG</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>0.8007111254060602</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.826831073737775</v>
+      </c>
+      <c r="D117" t="n">
+        <v>2.889072848494496</v>
+      </c>
+      <c r="E117" t="n">
+        <v>27.21857785124902</v>
+      </c>
+      <c r="F117" t="n">
+        <v>17.08771051689575</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈渔.JPG</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>-0.771088620424076</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6070553444496247</v>
+      </c>
+      <c r="D118" t="n">
+        <v>-1.215531138655375</v>
+      </c>
+      <c r="E118" t="n">
+        <v>-9.102328683301181</v>
+      </c>
+      <c r="F118" t="n">
+        <v>-8.30187015295237</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈玉婷.JPG</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>-0.7828368045077335</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1.740948094029886</v>
+      </c>
+      <c r="D119" t="n">
+        <v>-2.082191525481174</v>
+      </c>
+      <c r="E119" t="n">
+        <v>4.295090840654448</v>
+      </c>
+      <c r="F119" t="n">
+        <v>10.23272614442103</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈瑜.JPG</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1.729860435283638</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.694378101100068</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.269316870290694</v>
+      </c>
+      <c r="E120" t="n">
+        <v>-0.8845066364616121</v>
+      </c>
+      <c r="F120" t="n">
+        <v>-4.452812021096199</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈真.JPG</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>-2.094135163578439</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-1.7068937497462</v>
+      </c>
+      <c r="D121" t="n">
+        <v>-0.009370491843691551</v>
+      </c>
+      <c r="E121" t="n">
+        <v>-3.160433851896597</v>
+      </c>
+      <c r="F121" t="n">
+        <v>-4.259596660485133</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈米可.JPG</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1.020115468327242</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.88933287733005</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.7485136722590188</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-4.41890903027921</v>
+      </c>
+      <c r="F122" t="n">
+        <v>3.608017094812795</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈胤宇.JPG</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>-1.383921135276631</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-0.2644338714145247</v>
+      </c>
+      <c r="D123" t="n">
+        <v>-0.4018803993785503</v>
+      </c>
+      <c r="E123" t="n">
+        <v>9.461772492667164</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1.896366329185768</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈致豪.JPG</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>-1.286429093909283</v>
+      </c>
+      <c r="C124" t="n">
+        <v>2.165250139900469</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1.083232620419686</v>
+      </c>
+      <c r="E124" t="n">
+        <v>22.62576989300658</v>
+      </c>
+      <c r="F124" t="n">
+        <v>-11.22408681030083</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈芷萱.JPG</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>0.9703360875999826</v>
+      </c>
+      <c r="C125" t="n">
+        <v>3.967371519960678</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-0.2047177071088797</v>
+      </c>
+      <c r="E125" t="n">
+        <v>-1.477809393369485</v>
+      </c>
+      <c r="F125" t="n">
+        <v>-7.401443757965667</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈鑫慧.JPG</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>-1.447750208688551</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.3431835499812351</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-2.221970029492676</v>
+      </c>
+      <c r="E126" t="n">
+        <v>-8.975494041645256</v>
+      </c>
+      <c r="F126" t="n">
+        <v>-4.735365421075626</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈雪梅.JPG</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>-0.5683107481222885</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-2.278811232425491</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-1.20260900882391</v>
+      </c>
+      <c r="E127" t="n">
+        <v>-5.609504569229553</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.8554723077178408</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈露.JPG</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>-1.731870996597064</v>
+      </c>
+      <c r="C128" t="n">
+        <v>2.378870241496644</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-1.417672061261625</v>
+      </c>
+      <c r="E128" t="n">
+        <v>12.9763605272556</v>
+      </c>
+      <c r="F128" t="n">
+        <v>-1.861950961776869</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈靓靓.JPG</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1.216874275055201</v>
+      </c>
+      <c r="C129" t="n">
+        <v>3.383925060987135</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.7547958884799473</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.5065738687849005</v>
+      </c>
+      <c r="F129" t="n">
+        <v>6.296567655809397</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈静怡.JPG</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>0.5318804072521017</v>
+      </c>
+      <c r="C130" t="n">
+        <v>1.583604838940281</v>
+      </c>
+      <c r="D130" t="n">
+        <v>3.414423999342731</v>
+      </c>
+      <c r="E130" t="n">
+        <v>23.02524150003632</v>
+      </c>
+      <c r="F130" t="n">
+        <v>-2.079747329788129</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈韵旭.JPG</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>-0.888837186535621</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-1.833935877228109</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1.325527951706277</v>
+      </c>
+      <c r="E131" t="n">
+        <v>-2.603406299844734</v>
+      </c>
+      <c r="F131" t="n">
+        <v>-1.260611838981186</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>1.对称轴133张/陈麒文.JPG</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1.232166658774169</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-1.701816055714994</v>
+      </c>
+      <c r="D132" t="n">
+        <v>-2.281602472822903</v>
+      </c>
+      <c r="E132" t="n">
+        <v>-7.774186266823788</v>
+      </c>
+      <c r="F132" t="n">
+        <v>12.07417488570422</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/付彩萍.JPG</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>-0.9678391366557755</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.4647287088570246</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.8447207657147091</v>
+      </c>
+      <c r="E133" t="n">
+        <v>-2.8851480464805</v>
+      </c>
+      <c r="F133" t="n">
+        <v>-4.509392208985496</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/伏丹.JPG</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>-0.874492384170359</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-1.119776033176551</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.2215398706789168</v>
+      </c>
+      <c r="E134" t="n">
+        <v>16.20656503877936</v>
+      </c>
+      <c r="F134" t="n">
+        <v>-3.047599742994664</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何亮.JPG</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>-1.066477971531355</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1.564017221109735</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.208419642472878</v>
+      </c>
+      <c r="E135" t="n">
+        <v>-2.282288299454795</v>
+      </c>
+      <c r="F135" t="n">
+        <v>-9.559933843479874</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何俊梅.JPG</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1.54963856158294</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.4799535845563913</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1.380026281155868</v>
+      </c>
+      <c r="E136" t="n">
+        <v>-6.121472831047229</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1.227164988648069</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何婷.JPG</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>-0.7758758558681601</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.377327297867058</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-2.021676599361566</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-9.311594503367106</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-5.327776923487007</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何宸郡.JPG</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>-1.241110741124976</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.0820419103298857</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1.839043046760097</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-8.70578205876442</v>
+      </c>
+      <c r="F138" t="n">
+        <v>-6.035455408084036</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何晓清.JPG</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>-1.280496601903547</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.5284804063704454</v>
+      </c>
+      <c r="D139" t="n">
+        <v>-2.670629175429287</v>
+      </c>
+      <c r="E139" t="n">
+        <v>-8.883855647684086</v>
+      </c>
+      <c r="F139" t="n">
+        <v>-5.250301419496006</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何柠杉.JPG</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>-1.293838874424983</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-2.148176165573617</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1.55116307744826</v>
+      </c>
+      <c r="E140" t="n">
+        <v>3.611164502288053</v>
+      </c>
+      <c r="F140" t="n">
+        <v>5.454257542712218</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何欢.JPG</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1.209553125109096</v>
+      </c>
+      <c r="C141" t="n">
+        <v>1.977177679796339</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.128533673171539</v>
+      </c>
+      <c r="E141" t="n">
+        <v>-7.380825566510646</v>
+      </c>
+      <c r="F141" t="n">
+        <v>7.870131170883569</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何浩宇.JPG</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>-1.006011929480586</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.893048500911675</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.7643744223902069</v>
+      </c>
+      <c r="E142" t="n">
+        <v>-2.527156120407037</v>
+      </c>
+      <c r="F142" t="n">
+        <v>-4.106351457631049</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何涵璐.JPG</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>-0.9120558601640643</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.023401953275883</v>
+      </c>
+      <c r="D143" t="n">
+        <v>-0.8872982925508428</v>
+      </c>
+      <c r="E143" t="n">
+        <v>-3.308066436409982</v>
+      </c>
+      <c r="F143" t="n">
+        <v>-4.338077948367689</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何玙.JPG</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>-0.7762185704048901</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0.7581185342175428</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1.132331788510058</v>
+      </c>
+      <c r="E144" t="n">
+        <v>-2.655330002062988</v>
+      </c>
+      <c r="F144" t="n">
+        <v>-6.620998334476397</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何红春.JPG</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>-1.462364822245396</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-2.26811770124595</v>
+      </c>
+      <c r="D145" t="n">
+        <v>-1.356375809870454</v>
+      </c>
+      <c r="E145" t="n">
+        <v>6.050302777048825</v>
+      </c>
+      <c r="F145" t="n">
+        <v>-8.5822076945704</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何维.JPG</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>0.692415346607368</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-2.037049060459485</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1.43623407074712</v>
+      </c>
+      <c r="E146" t="n">
+        <v>19.12313824954094</v>
+      </c>
+      <c r="F146" t="n">
+        <v>7.547331476013704</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何美霖.JPG</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1.905777734982844</v>
+      </c>
+      <c r="C147" t="n">
+        <v>4.528822735720222</v>
+      </c>
+      <c r="D147" t="n">
+        <v>-1.404236460098086</v>
+      </c>
+      <c r="E147" t="n">
+        <v>14.42028247454234</v>
+      </c>
+      <c r="F147" t="n">
+        <v>7.845590263969294</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何苗.JPG</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>0.4397464439149869</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-1.552703039687726</v>
+      </c>
+      <c r="D148" t="n">
+        <v>-1.602064142077636</v>
+      </c>
+      <c r="E148" t="n">
+        <v>-4.267375959391334</v>
+      </c>
+      <c r="F148" t="n">
+        <v>4.441966779691557</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何莲花.JPG</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>-0.709563976679117</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0.04922368867892129</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1.490989671972828</v>
+      </c>
+      <c r="E149" t="n">
+        <v>6.381916159947069</v>
+      </c>
+      <c r="F149" t="n">
+        <v>2.844504538530124</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何蓉杰.JPG</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1.567670672257235</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-2.23319229095351</v>
+      </c>
+      <c r="D150" t="n">
+        <v>-2.35772443574931</v>
+      </c>
+      <c r="E150" t="n">
+        <v>-10.31973563461477</v>
+      </c>
+      <c r="F150" t="n">
+        <v>-4.258281561823029</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何蕊西.JPG</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>2.373556009973467</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0.472420218315279</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1.819718447032378</v>
+      </c>
+      <c r="E151" t="n">
+        <v>-1.469940543914088</v>
+      </c>
+      <c r="F151" t="n">
+        <v>-7.971184048957067</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何诺怡.JPG</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>-0.7439549868574219</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-2.824594958544499</v>
+      </c>
+      <c r="D152" t="n">
+        <v>-1.942307898015197</v>
+      </c>
+      <c r="E152" t="n">
+        <v>-9.760904270627293</v>
+      </c>
+      <c r="F152" t="n">
+        <v>-4.81616780350565</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何静.JPG</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>-0.2828086516565586</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.2812604881238455</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0.9614253706043463</v>
+      </c>
+      <c r="E153" t="n">
+        <v>-4.625823410320706</v>
+      </c>
+      <c r="F153" t="n">
+        <v>12.79470392861335</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/何静姝.JPG</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>-0.8036200178015286</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0.3085368687096399</v>
+      </c>
+      <c r="D154" t="n">
+        <v>-1.130700176256719</v>
+      </c>
+      <c r="E154" t="n">
+        <v>-2.828653223621097</v>
+      </c>
+      <c r="F154" t="n">
+        <v>-0.6951600352470105</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/侯博耀.JPG</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>-1.017791362515403</v>
+      </c>
+      <c r="C155" t="n">
+        <v>1.330565262460996</v>
+      </c>
+      <c r="D155" t="n">
+        <v>-1.917447509902394</v>
+      </c>
+      <c r="E155" t="n">
+        <v>8.784231884116032</v>
+      </c>
+      <c r="F155" t="n">
+        <v>6.683345141623946</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/侯蓉.JPG</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>0.8870416119856777</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-1.246543040863474</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1.561332337947984</v>
+      </c>
+      <c r="E156" t="n">
+        <v>1.218081607090288</v>
+      </c>
+      <c r="F156" t="n">
+        <v>-3.040342433710583</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/兰于青.JPG</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>0.5839893063707366</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0.1609763910915853</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0.1965676761446065</v>
+      </c>
+      <c r="E157" t="n">
+        <v>12.47857130387601</v>
+      </c>
+      <c r="F157" t="n">
+        <v>-5.467201261699618</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/兰亦成.JPG</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>-1.212491884660973</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-1.081885618579368</v>
+      </c>
+      <c r="D158" t="n">
+        <v>-2.517730886106798</v>
+      </c>
+      <c r="E158" t="n">
+        <v>-9.82216100030571</v>
+      </c>
+      <c r="F158" t="n">
+        <v>-10.05616052789728</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/兰添.JPG</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>1.167238257185775</v>
+      </c>
+      <c r="C159" t="n">
+        <v>2.745411036516847</v>
+      </c>
+      <c r="D159" t="n">
+        <v>-2.360481768231451</v>
+      </c>
+      <c r="E159" t="n">
+        <v>17.70046811067968</v>
+      </c>
+      <c r="F159" t="n">
+        <v>-0.09306555370086138</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/兰美慧.JPG</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>-0.2566338246868106</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.3815783536721821</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0.8543814636426361</v>
+      </c>
+      <c r="E160" t="n">
+        <v>-2.995875806722997</v>
+      </c>
+      <c r="F160" t="n">
+        <v>-2.609890062777381</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/冯仁强.JPG</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>0.9205519556537678</v>
+      </c>
+      <c r="C161" t="n">
+        <v>2.199430133271926</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1.928805111371795</v>
+      </c>
+      <c r="E161" t="n">
+        <v>12.78946828705924</v>
+      </c>
+      <c r="F161" t="n">
+        <v>-6.116185404906766</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/冯俐.JPG</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>-1.214792591421651</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-1.138443586978299</v>
+      </c>
+      <c r="D162" t="n">
+        <v>-2.522061776859478</v>
+      </c>
+      <c r="E162" t="n">
+        <v>-2.039705933114936</v>
+      </c>
+      <c r="F162" t="n">
+        <v>-0.7079260291757126</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/冯圣兰.JPG</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>0.5433790772129522</v>
+      </c>
+      <c r="C163" t="n">
+        <v>3.278296609981882</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0.2505832789845382</v>
+      </c>
+      <c r="E163" t="n">
+        <v>-3.499752594068029</v>
+      </c>
+      <c r="F163" t="n">
+        <v>11.77123037700525</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/冯思瑶.JPG</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>-1.409957504668718</v>
+      </c>
+      <c r="C164" t="n">
+        <v>1.400065326909801</v>
+      </c>
+      <c r="D164" t="n">
+        <v>-0.9504040475486139</v>
+      </c>
+      <c r="E164" t="n">
+        <v>-8.68969063406853</v>
+      </c>
+      <c r="F164" t="n">
+        <v>-4.632109724840602</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/冯梅.JPG</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>2.200795654655102</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.09375219232304258</v>
+      </c>
+      <c r="D165" t="n">
+        <v>2.005408488786394</v>
+      </c>
+      <c r="E165" t="n">
+        <v>-7.56945373695534</v>
+      </c>
+      <c r="F165" t="n">
+        <v>-0.405094798379784</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/冯浩林.JPG</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>-0.8610688286470762</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.6192862142533315</v>
+      </c>
+      <c r="D166" t="n">
+        <v>-0.8269556128136236</v>
+      </c>
+      <c r="E166" t="n">
+        <v>-6.877462945044006</v>
+      </c>
+      <c r="F166" t="n">
+        <v>-4.757322983458613</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/冯禹睿.JPG</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>1.09946997726003</v>
+      </c>
+      <c r="C167" t="n">
+        <v>0.0226947940694256</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1.457034743344464</v>
+      </c>
+      <c r="E167" t="n">
+        <v>-8.549730864219988</v>
+      </c>
+      <c r="F167" t="n">
+        <v>-4.469065234670637</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/冯耀杰.JPG</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>-0.133087901370372</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0.6465918008697981</v>
+      </c>
+      <c r="D168" t="n">
+        <v>1.172137179643794</v>
+      </c>
+      <c r="E168" t="n">
+        <v>15.07623160167502</v>
+      </c>
+      <c r="F168" t="n">
+        <v>12.9501974016317</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/古良玉.JPG</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>0.6887144196416162</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1.116040002002562</v>
+      </c>
+      <c r="D169" t="n">
+        <v>2.076617867455439</v>
+      </c>
+      <c r="E169" t="n">
+        <v>5.169423798401373</v>
+      </c>
+      <c r="F169" t="n">
+        <v>14.82127399494876</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/吉如意.JPG</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>-0.5198642655642233</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-1.15987376804369</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0.1453701680911997</v>
+      </c>
+      <c r="E170" t="n">
+        <v>5.135404560188703</v>
+      </c>
+      <c r="F170" t="n">
+        <v>7.519366721111252</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/吉方圆.JPG</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>-0.5694878088243396</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-2.898703848568054</v>
+      </c>
+      <c r="D171" t="n">
+        <v>-0.2789507213374515</v>
+      </c>
+      <c r="E171" t="n">
+        <v>-2.54445506737439</v>
+      </c>
+      <c r="F171" t="n">
+        <v>10.35366752855411</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/姜添.JPG</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>1.660215006525778</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-1.13699125324759</v>
+      </c>
+      <c r="D172" t="n">
+        <v>-1.26741220906455</v>
+      </c>
+      <c r="E172" t="n">
+        <v>-7.23013953310416</v>
+      </c>
+      <c r="F172" t="n">
+        <v>6.521398071340537</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/孔晨轩.JPG</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>-0.9666444605103878</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-1.247389183490428</v>
+      </c>
+      <c r="D173" t="n">
+        <v>-1.417351758738796</v>
+      </c>
+      <c r="E173" t="n">
+        <v>-9.535070345914024</v>
+      </c>
+      <c r="F173" t="n">
+        <v>-9.197307502229794</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/官昊融.JPG</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>0.1832404666556303</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-2.715386976720569</v>
+      </c>
+      <c r="D174" t="n">
+        <v>1.414254359291266</v>
+      </c>
+      <c r="E174" t="n">
+        <v>6.335211178581031</v>
+      </c>
+      <c r="F174" t="n">
+        <v>2.218084387975865</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/官露婷.JPG</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>-1.027601588965759</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-2.803067809422993</v>
+      </c>
+      <c r="D175" t="n">
+        <v>-1.004574580567727</v>
+      </c>
+      <c r="E175" t="n">
+        <v>-10.00906182076988</v>
+      </c>
+      <c r="F175" t="n">
+        <v>-10.90612411782363</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/巨熙.JPG</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>-1.643611080186772</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-0.4982389309896941</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0.9584248408748659</v>
+      </c>
+      <c r="E176" t="n">
+        <v>-8.310701580315094</v>
+      </c>
+      <c r="F176" t="n">
+        <v>-0.4963031669333229</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/康钟佩.JPG</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>2.094996456283321</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0.4241234410025849</v>
+      </c>
+      <c r="D177" t="n">
+        <v>-0.3173948164007692</v>
+      </c>
+      <c r="E177" t="n">
+        <v>-0.9362026088212249</v>
+      </c>
+      <c r="F177" t="n">
+        <v>-6.484285722947223</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/敬俊.JPG</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>1.411699442755896</v>
+      </c>
+      <c r="C178" t="n">
+        <v>2.119066785973871</v>
+      </c>
+      <c r="D178" t="n">
+        <v>1.131185774654514</v>
+      </c>
+      <c r="E178" t="n">
+        <v>-4.230579230815406</v>
+      </c>
+      <c r="F178" t="n">
+        <v>7.678197309880991</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/敬小耘.JPG</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>-1.545197259236431</v>
+      </c>
+      <c r="C179" t="n">
+        <v>0.7858969751379175</v>
+      </c>
+      <c r="D179" t="n">
+        <v>-2.300140615394852</v>
+      </c>
+      <c r="E179" t="n">
+        <v>-8.436460864035407</v>
+      </c>
+      <c r="F179" t="n">
+        <v>-6.780361487354551</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/景光州.JPG</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>-1.039745947275647</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-1.300532047057987</v>
+      </c>
+      <c r="D180" t="n">
+        <v>2.032422344038782</v>
+      </c>
+      <c r="E180" t="n">
+        <v>18.71872491279987</v>
+      </c>
+      <c r="F180" t="n">
+        <v>7.698700819944944</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李丽偲.JPG</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>-0.795939195343033</v>
+      </c>
+      <c r="C181" t="n">
+        <v>2.884657053773798</v>
+      </c>
+      <c r="D181" t="n">
+        <v>-1.949462261405734</v>
+      </c>
+      <c r="E181" t="n">
+        <v>-2.942532686641893</v>
+      </c>
+      <c r="F181" t="n">
+        <v>-11.01548616126659</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李伯忱.JPG</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>1.4354520075887</v>
+      </c>
+      <c r="C182" t="n">
+        <v>1.858204360797931</v>
+      </c>
+      <c r="D182" t="n">
+        <v>-2.434828078866736</v>
+      </c>
+      <c r="E182" t="n">
+        <v>2.104245545914032</v>
+      </c>
+      <c r="F182" t="n">
+        <v>-7.117670419650718</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李佳.JPG</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>-1.11752809965985</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-0.6360933152621631</v>
+      </c>
+      <c r="D183" t="n">
+        <v>-1.054566940993657</v>
+      </c>
+      <c r="E183" t="n">
+        <v>-11.05276087571997</v>
+      </c>
+      <c r="F183" t="n">
+        <v>-13.31781401924762</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李佳镁.JPG</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>2.487104157850433</v>
+      </c>
+      <c r="C184" t="n">
+        <v>3.879148912336383</v>
+      </c>
+      <c r="D184" t="n">
+        <v>-0.0472792555258215</v>
+      </c>
+      <c r="E184" t="n">
+        <v>2.190135805160791</v>
+      </c>
+      <c r="F184" t="n">
+        <v>-3.671206204038526</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李俊豪.JPG</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>0.7881948591189855</v>
+      </c>
+      <c r="C185" t="n">
+        <v>1.672961722541943</v>
+      </c>
+      <c r="D185" t="n">
+        <v>1.125527097446879</v>
+      </c>
+      <c r="E185" t="n">
+        <v>4.498761209174039</v>
+      </c>
+      <c r="F185" t="n">
+        <v>17.89662519416788</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李冬欣.JPG</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>0.370447229763243</v>
+      </c>
+      <c r="C186" t="n">
+        <v>1.519048531191366</v>
+      </c>
+      <c r="D186" t="n">
+        <v>-0.7620755891752418</v>
+      </c>
+      <c r="E186" t="n">
+        <v>10.5230362139453</v>
+      </c>
+      <c r="F186" t="n">
+        <v>6.143280363391922</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李博.JPG</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>1.57707210987384</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.6187176294307976</v>
+      </c>
+      <c r="D187" t="n">
+        <v>-2.405696119040062</v>
+      </c>
+      <c r="E187" t="n">
+        <v>-0.7873744517973086</v>
+      </c>
+      <c r="F187" t="n">
+        <v>-8.605713827155641</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李嘉惠.JPG</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>-0.7206510735793967</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-2.30102306539175</v>
+      </c>
+      <c r="D188" t="n">
+        <v>4.023082425637951</v>
+      </c>
+      <c r="E188" t="n">
+        <v>-2.52245032834492</v>
+      </c>
+      <c r="F188" t="n">
+        <v>6.321445457461377</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李孟阳.JPG</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>-0.2668371941491942</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0.1102554823966636</v>
+      </c>
+      <c r="D189" t="n">
+        <v>-1.990992478242649</v>
+      </c>
+      <c r="E189" t="n">
+        <v>-3.545724275235764</v>
+      </c>
+      <c r="F189" t="n">
+        <v>-0.01296478565246688</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李昌朔.JPG</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>-0.3178546590806939</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-2.155916134026939</v>
+      </c>
+      <c r="D190" t="n">
+        <v>-2.050785240990123</v>
+      </c>
+      <c r="E190" t="n">
+        <v>-3.559429859506354</v>
+      </c>
+      <c r="F190" t="n">
+        <v>-0.156444023945938</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李晨语.JPG</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>0.7066665532161247</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-0.9968297510802683</v>
+      </c>
+      <c r="D191" t="n">
+        <v>1.420707636420006</v>
+      </c>
+      <c r="E191" t="n">
+        <v>-9.945261660199657</v>
+      </c>
+      <c r="F191" t="n">
+        <v>-9.086546029239548</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李林蔚.JPG</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>0.1405796790762105</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0.3346651804435002</v>
+      </c>
+      <c r="D192" t="n">
+        <v>-1.819023771155956</v>
+      </c>
+      <c r="E192" t="n">
+        <v>-8.447787236053738</v>
+      </c>
+      <c r="F192" t="n">
+        <v>-0.02803043652671579</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李果.JPG</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>2.75522642508762</v>
+      </c>
+      <c r="C193" t="n">
+        <v>4.308004620435231</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0.1668830465689477</v>
+      </c>
+      <c r="E193" t="n">
+        <v>10.08293115754282</v>
+      </c>
+      <c r="F193" t="n">
+        <v>-1.188475167184742</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李柯兴.JPG</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>-0.5063613665318307</v>
+      </c>
+      <c r="C194" t="n">
+        <v>1.040333134809607</v>
+      </c>
+      <c r="D194" t="n">
+        <v>1.52033272521149</v>
+      </c>
+      <c r="E194" t="n">
+        <v>-9.688523079026174</v>
+      </c>
+      <c r="F194" t="n">
+        <v>-10.39787799868008</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李柳梅.JPG</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>-1.375402920182758</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.9592569976327965</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0.3630389262344384</v>
+      </c>
+      <c r="E195" t="n">
+        <v>-8.682175194717175</v>
+      </c>
+      <c r="F195" t="n">
+        <v>-8.014967064584976</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李梅.JPG</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>-0.9137605928351339</v>
+      </c>
+      <c r="C196" t="n">
+        <v>2.202979647232807</v>
+      </c>
+      <c r="D196" t="n">
+        <v>2.087812139042918</v>
+      </c>
+      <c r="E196" t="n">
+        <v>-1.260492203124195</v>
+      </c>
+      <c r="F196" t="n">
+        <v>-7.372802241199721</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李海升.JPG</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>1.983680200828944</v>
+      </c>
+      <c r="C197" t="n">
+        <v>1.635986742982194</v>
+      </c>
+      <c r="D197" t="n">
+        <v>-1.726608067634266</v>
+      </c>
+      <c r="E197" t="n">
+        <v>-9.133718672421178</v>
+      </c>
+      <c r="F197" t="n">
+        <v>-3.756436787972452</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李海树.JPG</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1.177466257106379</v>
+      </c>
+      <c r="C198" t="n">
+        <v>2.982579395232996</v>
+      </c>
+      <c r="D198" t="n">
+        <v>-0.399824327549465</v>
+      </c>
+      <c r="E198" t="n">
+        <v>-1.43527031100862</v>
+      </c>
+      <c r="F198" t="n">
+        <v>-8.765380931331315</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李璐杉.JPG</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>-2.664546718155016</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-0.9337071425640008</v>
+      </c>
+      <c r="D199" t="n">
+        <v>-2.359452353897014</v>
+      </c>
+      <c r="E199" t="n">
+        <v>-3.577954976303653</v>
+      </c>
+      <c r="F199" t="n">
+        <v>-8.480602059963598</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李翠莲.JPG</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>-0.8954603574698842</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.619073272286344</v>
+      </c>
+      <c r="D200" t="n">
+        <v>1.992022374343219</v>
+      </c>
+      <c r="E200" t="n">
+        <v>-9.750355987766479</v>
+      </c>
+      <c r="F200" t="n">
+        <v>-10.33422934103724</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李艾凌.JPG</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>0.2099093403913828</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0.2981333425210702</v>
+      </c>
+      <c r="D201" t="n">
+        <v>-0.8237816005764621</v>
+      </c>
+      <c r="E201" t="n">
+        <v>-9.09296244695682</v>
+      </c>
+      <c r="F201" t="n">
+        <v>-4.053395219595848</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李艾恬.JPG</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>-1.052643576637685</v>
+      </c>
+      <c r="C202" t="n">
+        <v>-0.08857745873351075</v>
+      </c>
+      <c r="D202" t="n">
+        <v>2.198872418206108</v>
+      </c>
+      <c r="E202" t="n">
+        <v>11.41652552881575</v>
+      </c>
+      <c r="F202" t="n">
+        <v>15.84705983746595</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李莉.JPG</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>-1.068795439655258</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0.01556424869487888</v>
+      </c>
+      <c r="D203" t="n">
+        <v>1.301959851314748</v>
+      </c>
+      <c r="E203" t="n">
+        <v>-2.456974151619575</v>
+      </c>
+      <c r="F203" t="n">
+        <v>-0.6213510929515202</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李蔓青.JPG</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>-1.182975314724452</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0.203370643641678</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0.09620175537353139</v>
+      </c>
+      <c r="E204" t="n">
+        <v>-1.894949438225718</v>
+      </c>
+      <c r="F204" t="n">
+        <v>-4.194577563615129</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李蕾.JPG</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>-2.436472734758713</v>
+      </c>
+      <c r="C205" t="n">
+        <v>-0.6761764650731691</v>
+      </c>
+      <c r="D205" t="n">
+        <v>-0.967442194957907</v>
+      </c>
+      <c r="E205" t="n">
+        <v>-8.367307780199239</v>
+      </c>
+      <c r="F205" t="n">
+        <v>-0.06469740922766366</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李金春.JPG</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>0.1258745155933421</v>
+      </c>
+      <c r="C206" t="n">
+        <v>1.197261691971876</v>
+      </c>
+      <c r="D206" t="n">
+        <v>-0.4339514631567223</v>
+      </c>
+      <c r="E206" t="n">
+        <v>-3.012833819948165</v>
+      </c>
+      <c r="F206" t="n">
+        <v>12.24988582465621</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李金铭.JPG</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>0.3849574740621157</v>
+      </c>
+      <c r="C207" t="n">
+        <v>-0.3729456156478705</v>
+      </c>
+      <c r="D207" t="n">
+        <v>1.056521699114013</v>
+      </c>
+      <c r="E207" t="n">
+        <v>3.932978827503066</v>
+      </c>
+      <c r="F207" t="n">
+        <v>3.235557697418536</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/李锦烨.JPG</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>0.9551957916619399</v>
+      </c>
+      <c r="C208" t="n">
+        <v>-2.658828061884877</v>
+      </c>
+      <c r="D208" t="n">
+        <v>-2.128060164090889</v>
+      </c>
+      <c r="E208" t="n">
+        <v>-4.762724871110721</v>
+      </c>
+      <c r="F208" t="n">
+        <v>11.24898738787447</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/柯倩.JPG</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>0.9558943732926624</v>
+      </c>
+      <c r="C209" t="n">
+        <v>-1.640643777254893</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0.00240769036068228</v>
+      </c>
+      <c r="E209" t="n">
+        <v>-7.506510437947556</v>
+      </c>
+      <c r="F209" t="n">
+        <v>12.37508890066589</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/江旭刚.JPG</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>2.410880665289119</v>
+      </c>
+      <c r="C210" t="n">
+        <v>-0.9604281971932095</v>
+      </c>
+      <c r="D210" t="n">
+        <v>-0.816097815642343</v>
+      </c>
+      <c r="E210" t="n">
+        <v>-2.360910545037756</v>
+      </c>
+      <c r="F210" t="n">
+        <v>-5.218040691632472</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/江明月.JPG</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>1.733044813756734</v>
+      </c>
+      <c r="C211" t="n">
+        <v>-1.66716777021854</v>
+      </c>
+      <c r="D211" t="n">
+        <v>3.018613243255905</v>
+      </c>
+      <c r="E211" t="n">
+        <v>-2.090675475286686</v>
+      </c>
+      <c r="F211" t="n">
+        <v>-2.553411395724123</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/江浩宇.JPG</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>-0.4872830953477408</v>
+      </c>
+      <c r="C212" t="n">
+        <v>-2.3092079808158</v>
+      </c>
+      <c r="D212" t="n">
+        <v>-2.572644139245415</v>
+      </c>
+      <c r="E212" t="n">
+        <v>-1.907765602910934</v>
+      </c>
+      <c r="F212" t="n">
+        <v>-6.057695765896821</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/江知晓.JPG</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>0.7896634690659843</v>
+      </c>
+      <c r="C213" t="n">
+        <v>-1.111521982692765</v>
+      </c>
+      <c r="D213" t="n">
+        <v>-0.04953956041392248</v>
+      </c>
+      <c r="E213" t="n">
+        <v>-2.699390221264194</v>
+      </c>
+      <c r="F213" t="n">
+        <v>-7.417141622245099</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/江竞航.JPG</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>-0.5533201407464273</v>
+      </c>
+      <c r="C214" t="n">
+        <v>-0.3706743698788597</v>
+      </c>
+      <c r="D214" t="n">
+        <v>-1.772957881519379</v>
+      </c>
+      <c r="E214" t="n">
+        <v>-4.433563091861735</v>
+      </c>
+      <c r="F214" t="n">
+        <v>-6.573247766876875</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/江鑫锐.JPG</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>-1.450058614012</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0.9048084691136247</v>
+      </c>
+      <c r="D215" t="n">
+        <v>-1.636530256365059</v>
+      </c>
+      <c r="E215" t="n">
+        <v>9.328471672694565</v>
+      </c>
+      <c r="F215" t="n">
+        <v>5.947878811018821</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/管梓岑.JPG</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>-0.9723701242641868</v>
+      </c>
+      <c r="C216" t="n">
+        <v>-2.418244184140181</v>
+      </c>
+      <c r="D216" t="n">
+        <v>-1.57942472826357</v>
+      </c>
+      <c r="E216" t="n">
+        <v>-3.529098347590075</v>
+      </c>
+      <c r="F216" t="n">
+        <v>4.554540800041309</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/胡峻铭.JPG</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>-0.7920555909960489</v>
+      </c>
+      <c r="C217" t="n">
+        <v>-0.01579733180991586</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0.592724145610226</v>
+      </c>
+      <c r="E217" t="n">
+        <v>-2.99051216900976</v>
+      </c>
+      <c r="F217" t="n">
+        <v>-9.250622304677867</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/胡晓.JPG</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>-2.110737904643415</v>
+      </c>
+      <c r="C218" t="n">
+        <v>-1.907518923360699</v>
+      </c>
+      <c r="D218" t="n">
+        <v>-0.1367031154907692</v>
+      </c>
+      <c r="E218" t="n">
+        <v>-4.282396359716718</v>
+      </c>
+      <c r="F218" t="n">
+        <v>-0.5880736143384334</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/胡晓毅.JPG</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>-0.3257039001385153</v>
+      </c>
+      <c r="C219" t="n">
+        <v>2.488414176075648</v>
+      </c>
+      <c r="D219" t="n">
+        <v>-0.7627440750570004</v>
+      </c>
+      <c r="E219" t="n">
+        <v>21.96056566622283</v>
+      </c>
+      <c r="F219" t="n">
+        <v>-0.5276284513197138</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/胡晖楠.JPG</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>-1.494247977870264</v>
+      </c>
+      <c r="C220" t="n">
+        <v>-0.3955846516322888</v>
+      </c>
+      <c r="D220" t="n">
+        <v>2.715938157110719</v>
+      </c>
+      <c r="E220" t="n">
+        <v>-4.209678539457482</v>
+      </c>
+      <c r="F220" t="n">
+        <v>7.121476427632599</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/胡浩洋.JPG</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>-0.6778903511065301</v>
+      </c>
+      <c r="C221" t="n">
+        <v>-2.767938674231754</v>
+      </c>
+      <c r="D221" t="n">
+        <v>1.563418887815758</v>
+      </c>
+      <c r="E221" t="n">
+        <v>-4.334670259690896</v>
+      </c>
+      <c r="F221" t="n">
+        <v>4.630817146329965</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/胡芷毓.JPG</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>-1.212106862352416</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0.6617013481403015</v>
+      </c>
+      <c r="D222" t="n">
+        <v>-0.3730104514398125</v>
+      </c>
+      <c r="E222" t="n">
+        <v>17.27418393875807</v>
+      </c>
+      <c r="F222" t="n">
+        <v>3.453802109343705</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/花语.JPG</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>-0.1018480389027718</v>
+      </c>
+      <c r="C223" t="n">
+        <v>1.304430665510494</v>
+      </c>
+      <c r="D223" t="n">
+        <v>-1.721955340236831</v>
+      </c>
+      <c r="E223" t="n">
+        <v>13.50452079956796</v>
+      </c>
+      <c r="F223" t="n">
+        <v>-8.293078003488819</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/蒋明明.JPG</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>0.4360509560195695</v>
+      </c>
+      <c r="C224" t="n">
+        <v>2.088246623304055</v>
+      </c>
+      <c r="D224" t="n">
+        <v>4.194967408781326</v>
+      </c>
+      <c r="E224" t="n">
+        <v>17.90330732104381</v>
+      </c>
+      <c r="F224" t="n">
+        <v>17.3978311066342</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/蒋洪.JPG</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>-0.1532188830964449</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0.5083774118987413</v>
+      </c>
+      <c r="D225" t="n">
+        <v>-1.434489298616359</v>
+      </c>
+      <c r="E225" t="n">
+        <v>5.589924393493919</v>
+      </c>
+      <c r="F225" t="n">
+        <v>14.97730979210344</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/蒋雅竹.JPG</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>-0.250140933118535</v>
+      </c>
+      <c r="C226" t="n">
+        <v>-0.2506854366911719</v>
+      </c>
+      <c r="D226" t="n">
+        <v>-0.09479863876595843</v>
+      </c>
+      <c r="E226" t="n">
+        <v>-7.449898071587006</v>
+      </c>
+      <c r="F226" t="n">
+        <v>-0.9374068373872928</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/解陈群.JPG</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>0.01938125079701382</v>
+      </c>
+      <c r="C227" t="n">
+        <v>-0.4641816955028881</v>
+      </c>
+      <c r="D227" t="n">
+        <v>-0.7672613332288587</v>
+      </c>
+      <c r="E227" t="n">
+        <v>-0.3430003489880706</v>
+      </c>
+      <c r="F227" t="n">
+        <v>0.05463220937274736</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/谷俊杰.JPG</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>1.700389906407643</v>
+      </c>
+      <c r="C228" t="n">
+        <v>1.755727951031157</v>
+      </c>
+      <c r="D228" t="n">
+        <v>2.836162079779683</v>
+      </c>
+      <c r="E228" t="n">
+        <v>26.53751318458151</v>
+      </c>
+      <c r="F228" t="n">
+        <v>16.9556102939831</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/贺冬梅.JPG</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>2.154551050370322</v>
+      </c>
+      <c r="C229" t="n">
+        <v>-0.2061359336048088</v>
+      </c>
+      <c r="D229" t="n">
+        <v>-0.9771319526199842</v>
+      </c>
+      <c r="E229" t="n">
+        <v>-2.243269744865352</v>
+      </c>
+      <c r="F229" t="n">
+        <v>-5.263443336830187</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/贺宇翔.JPG</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>0.8064936170881577</v>
+      </c>
+      <c r="C230" t="n">
+        <v>4.543938754517971</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0.3223035812716509</v>
+      </c>
+      <c r="E230" t="n">
+        <v>-2.858849327827337</v>
+      </c>
+      <c r="F230" t="n">
+        <v>12.5890167907328</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/贺灿.JPG</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>-1.017900172907487</v>
+      </c>
+      <c r="C231" t="n">
+        <v>-0.3762140729637656</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0.3988827493435002</v>
+      </c>
+      <c r="E231" t="n">
+        <v>-8.69398949430926</v>
+      </c>
+      <c r="F231" t="n">
+        <v>-12.72454226004646</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/贺露.JPG</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>0.358386582134162</v>
+      </c>
+      <c r="C232" t="n">
+        <v>-0.993386038326323</v>
+      </c>
+      <c r="D232" t="n">
+        <v>-0.56302596650064</v>
+      </c>
+      <c r="E232" t="n">
+        <v>-2.593767971074286</v>
+      </c>
+      <c r="F232" t="n">
+        <v>-10.82446985711623</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/贾愔棋.JPG</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>-1.583044381611163</v>
+      </c>
+      <c r="C233" t="n">
+        <v>1.950325832826601</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0.5197346298452978</v>
+      </c>
+      <c r="E233" t="n">
+        <v>-3.931868178679418</v>
+      </c>
+      <c r="F233" t="n">
+        <v>7.938588846735345</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/贾浩宇.JPG</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>-0.9753109859605239</v>
+      </c>
+      <c r="C234" t="n">
+        <v>-1.710786647151486</v>
+      </c>
+      <c r="D234" t="n">
+        <v>-0.4807097612099874</v>
+      </c>
+      <c r="E234" t="n">
+        <v>-3.326957894022326</v>
+      </c>
+      <c r="F234" t="n">
+        <v>-1.823331295872398</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/贾茹.JPG</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>-1.310988551697797</v>
+      </c>
+      <c r="C235" t="n">
+        <v>-1.575351126991773</v>
+      </c>
+      <c r="D235" t="n">
+        <v>-1.877239354631679</v>
+      </c>
+      <c r="E235" t="n">
+        <v>-1.903930784942711</v>
+      </c>
+      <c r="F235" t="n">
+        <v>-3.883753432619443</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/赖俊颖.JPG</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>0.9631715035820211</v>
+      </c>
+      <c r="C236" t="n">
+        <v>-0.7340088137434734</v>
+      </c>
+      <c r="D236" t="n">
+        <v>-2.309174517146567</v>
+      </c>
+      <c r="E236" t="n">
+        <v>-9.729286416228685</v>
+      </c>
+      <c r="F236" t="n">
+        <v>-11.08363167401328</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/赖婷.JPG</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>3.697335934925114</v>
+      </c>
+      <c r="C237" t="n">
+        <v>3.453612395230601</v>
+      </c>
+      <c r="D237" t="n">
+        <v>-1.038884929810524</v>
+      </c>
+      <c r="E237" t="n">
+        <v>23.23503299992252</v>
+      </c>
+      <c r="F237" t="n">
+        <v>1.268307015515446</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/赖巧.JPG</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>-1.267224572978881</v>
+      </c>
+      <c r="C238" t="n">
+        <v>1.418803591367998</v>
+      </c>
+      <c r="D238" t="n">
+        <v>-0.8968276238023841</v>
+      </c>
+      <c r="E238" t="n">
+        <v>-0.9145918654861217</v>
+      </c>
+      <c r="F238" t="n">
+        <v>-8.470589446650628</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/郭优美.JPG</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>1.107649451363293</v>
+      </c>
+      <c r="C239" t="n">
+        <v>-0.3158656266931993</v>
+      </c>
+      <c r="D239" t="n">
+        <v>-0.6908882950527558</v>
+      </c>
+      <c r="E239" t="n">
+        <v>-9.407871903243436</v>
+      </c>
+      <c r="F239" t="n">
+        <v>-12.22928687725706</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/郭子雅.JPG</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>-0.06459943428610802</v>
+      </c>
+      <c r="C240" t="n">
+        <v>-1.779141619778007</v>
+      </c>
+      <c r="D240" t="n">
+        <v>-2.14812198476972</v>
+      </c>
+      <c r="E240" t="n">
+        <v>-8.479060127125825</v>
+      </c>
+      <c r="F240" t="n">
+        <v>14.0138265817431</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/郭晶.JPG</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>-0.3447020604038564</v>
+      </c>
+      <c r="C241" t="n">
+        <v>1.091814223550249</v>
+      </c>
+      <c r="D241" t="n">
+        <v>-2.110300218088482</v>
+      </c>
+      <c r="E241" t="n">
+        <v>-9.538866737748734</v>
+      </c>
+      <c r="F241" t="n">
+        <v>-11.64420845819256</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/郭燕.JPG</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>-1.270012960607805</v>
+      </c>
+      <c r="C242" t="n">
+        <v>-1.741052035140037</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0.1023451071229635</v>
+      </c>
+      <c r="E242" t="n">
+        <v>-6.536313312780464</v>
+      </c>
+      <c r="F242" t="n">
+        <v>-3.858730049477944</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/郭达.JPG</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>-1.016519718336496</v>
+      </c>
+      <c r="C243" t="n">
+        <v>-2.170042219765404</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0.6613096022789314</v>
+      </c>
+      <c r="E243" t="n">
+        <v>-8.146588360927414</v>
+      </c>
+      <c r="F243" t="n">
+        <v>6.049744112533618</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/郭露.JPG</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>-1.188504420402514</v>
+      </c>
+      <c r="C244" t="n">
+        <v>1.1448116993733</v>
+      </c>
+      <c r="D244" t="n">
+        <v>-1.039696280672201</v>
+      </c>
+      <c r="E244" t="n">
+        <v>-8.733071225356174</v>
+      </c>
+      <c r="F244" t="n">
+        <v>-8.836469690492429</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/金浩苒.JPG</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>1.190161952282011</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0.01832728616741081</v>
+      </c>
+      <c r="D245" t="n">
+        <v>-0.799546809323866</v>
+      </c>
+      <c r="E245" t="n">
+        <v>12.19314123038984</v>
+      </c>
+      <c r="F245" t="n">
+        <v>-5.215013577065345</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/雷丽.JPG</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>-0.6168416543777486</v>
+      </c>
+      <c r="C246" t="n">
+        <v>-1.180817494153912</v>
+      </c>
+      <c r="D246" t="n">
+        <v>2.266783364800325</v>
+      </c>
+      <c r="E246" t="n">
+        <v>6.738280519337168</v>
+      </c>
+      <c r="F246" t="n">
+        <v>10.33716534684391</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/雷诗琪.JPG</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>-0.896813601574649</v>
+      </c>
+      <c r="C247" t="n">
+        <v>1.700562298733672</v>
+      </c>
+      <c r="D247" t="n">
+        <v>-1.646820940470497</v>
+      </c>
+      <c r="E247" t="n">
+        <v>-4.770935353132656</v>
+      </c>
+      <c r="F247" t="n">
+        <v>-4.251422321105853</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/雷雯.JPG</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>-1.041079341797957</v>
+      </c>
+      <c r="C248" t="n">
+        <v>1.071577652432549</v>
+      </c>
+      <c r="D248" t="n">
+        <v>-1.99434385345288</v>
+      </c>
+      <c r="E248" t="n">
+        <v>-8.619533134960296</v>
+      </c>
+      <c r="F248" t="n">
+        <v>-4.810384573104713</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/韩俊.JPG</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>-1.188812466151154</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0.4998488763293539</v>
+      </c>
+      <c r="D249" t="n">
+        <v>-0.2598257529973129</v>
+      </c>
+      <c r="E249" t="n">
+        <v>-8.529896527571928</v>
+      </c>
+      <c r="F249" t="n">
+        <v>-5.568410713825597</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/韩知彤.JPG</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>2.083821532151682</v>
+      </c>
+      <c r="C250" t="n">
+        <v>1.016334870220021</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0.1195062293611438</v>
+      </c>
+      <c r="E250" t="n">
+        <v>-8.111516759061059</v>
+      </c>
+      <c r="F250" t="n">
+        <v>-5.8127424568885</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/顾振西.JPG</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>-0.5400585521445421</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.9958083186259588</v>
+      </c>
+      <c r="D251" t="n">
+        <v>-0.903941672560453</v>
+      </c>
+      <c r="E251" t="n">
+        <v>-3.278261757697662</v>
+      </c>
+      <c r="F251" t="n">
+        <v>13.26852374622658</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/高妍妍.JPG</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>2.926516638705158</v>
+      </c>
+      <c r="C252" t="n">
+        <v>2.567174823323881</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.5398630758474716</v>
+      </c>
+      <c r="E252" t="n">
+        <v>7.206459709796482</v>
+      </c>
+      <c r="F252" t="n">
+        <v>-9.152944165223159</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/高小果.JPG</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>-1.657112525305743</v>
+      </c>
+      <c r="C253" t="n">
+        <v>-0.5145966175013994</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0.1621395534754649</v>
+      </c>
+      <c r="E253" t="n">
+        <v>-3.208318328698241</v>
+      </c>
+      <c r="F253" t="n">
+        <v>-4.218375332853523</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/高文婷.JPG</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>-1.390745683131432</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0.05526725058444821</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0.1583180483541842</v>
+      </c>
+      <c r="E254" t="n">
+        <v>-8.329339493376128</v>
+      </c>
+      <c r="F254" t="n">
+        <v>-4.865596706647679</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/高文桢.JPG</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>1.791921032487252</v>
+      </c>
+      <c r="C255" t="n">
+        <v>2.685062817360325</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0.264637673425388</v>
+      </c>
+      <c r="E255" t="n">
+        <v>-1.708105794047071</v>
+      </c>
+      <c r="F255" t="n">
+        <v>-10.89061231344265</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/高春梅.JPG</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>1.132316190389292</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0.02234216325199719</v>
+      </c>
+      <c r="D256" t="n">
+        <v>1.688093483075924</v>
+      </c>
+      <c r="E256" t="n">
+        <v>13.33926083522682</v>
+      </c>
+      <c r="F256" t="n">
+        <v>-1.804109256160636</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/高林静.JPG</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>-0.6841352432993328</v>
+      </c>
+      <c r="C257" t="n">
+        <v>1.535638111285713</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0.3821599046062524</v>
+      </c>
+      <c r="E257" t="n">
+        <v>-4.091473163200156</v>
+      </c>
+      <c r="F257" t="n">
+        <v>17.71154713972419</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/高雨洁.JPG</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>0.4689598130080342</v>
+      </c>
+      <c r="C258" t="n">
+        <v>-1.064479824283975</v>
+      </c>
+      <c r="D258" t="n">
+        <v>0.5091153281176397</v>
+      </c>
+      <c r="E258" t="n">
+        <v>11.51451486906269</v>
+      </c>
+      <c r="F258" t="n">
+        <v>-6.082706770121273</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/高静文.JPG</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>-0.6167064963443264</v>
+      </c>
+      <c r="C259" t="n">
+        <v>-1.707729616540955</v>
+      </c>
+      <c r="D259" t="n">
+        <v>-2.587633977598971</v>
+      </c>
+      <c r="E259" t="n">
+        <v>-3.210733331916146</v>
+      </c>
+      <c r="F259" t="n">
+        <v>-10.54262649514967</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄博.JPG</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>-1.321353950730312</v>
+      </c>
+      <c r="C260" t="n">
+        <v>-1.524022864670997</v>
+      </c>
+      <c r="D260" t="n">
+        <v>-3.239982399198885</v>
+      </c>
+      <c r="E260" t="n">
+        <v>6.667356884223755</v>
+      </c>
+      <c r="F260" t="n">
+        <v>-5.833260920507034</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄卫.JPG</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>0.09629652344173223</v>
+      </c>
+      <c r="C261" t="n">
+        <v>-1.440816679427802</v>
+      </c>
+      <c r="D261" t="n">
+        <v>2.629479736610161</v>
+      </c>
+      <c r="E261" t="n">
+        <v>18.72484170313433</v>
+      </c>
+      <c r="F261" t="n">
+        <v>8.08143546535808</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄媛.JPG</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>-0.5333081163332832</v>
+      </c>
+      <c r="C262" t="n">
+        <v>-0.1384486248432181</v>
+      </c>
+      <c r="D262" t="n">
+        <v>0.6927433052038834</v>
+      </c>
+      <c r="E262" t="n">
+        <v>-1.202233269116809</v>
+      </c>
+      <c r="F262" t="n">
+        <v>-6.651683212460552</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄子淇.JPG</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>0.6907706803770721</v>
+      </c>
+      <c r="C263" t="n">
+        <v>3.719300904936047</v>
+      </c>
+      <c r="D263" t="n">
+        <v>-1.116770855654332</v>
+      </c>
+      <c r="E263" t="n">
+        <v>6.959721871084744</v>
+      </c>
+      <c r="F263" t="n">
+        <v>-0.6142858516270325</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄志婉.JPG</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>0.9111774983820979</v>
+      </c>
+      <c r="C264" t="n">
+        <v>-0.1766193976771701</v>
+      </c>
+      <c r="D264" t="n">
+        <v>2.109920305099238</v>
+      </c>
+      <c r="E264" t="n">
+        <v>-7.312388775404978</v>
+      </c>
+      <c r="F264" t="n">
+        <v>1.115813785384082</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄思敏.JPG</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>-1.800371908875013</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0.9493233832044684</v>
+      </c>
+      <c r="D265" t="n">
+        <v>-0.5250989186546081</v>
+      </c>
+      <c r="E265" t="n">
+        <v>-4.24233775791564</v>
+      </c>
+      <c r="F265" t="n">
+        <v>-4.062778048642627</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄朝民.JPG</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>-1.498975780700549</v>
+      </c>
+      <c r="C266" t="n">
+        <v>-2.602673608289505</v>
+      </c>
+      <c r="D266" t="n">
+        <v>-1.154898437252663</v>
+      </c>
+      <c r="E266" t="n">
+        <v>-9.516253080326615</v>
+      </c>
+      <c r="F266" t="n">
+        <v>-7.565129010980686</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄柳依.JPG</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>1.003147410083049</v>
+      </c>
+      <c r="C267" t="n">
+        <v>-0.8289298901961714</v>
+      </c>
+      <c r="D267" t="n">
+        <v>1.667523847669071</v>
+      </c>
+      <c r="E267" t="n">
+        <v>-4.279780599161891</v>
+      </c>
+      <c r="F267" t="n">
+        <v>4.970109314055815</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄楷译.JPG</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>-1.022184467217282</v>
+      </c>
+      <c r="C268" t="n">
+        <v>-1.282362317301109</v>
+      </c>
+      <c r="D268" t="n">
+        <v>1.160517717133126</v>
+      </c>
+      <c r="E268" t="n">
+        <v>20.45828207586539</v>
+      </c>
+      <c r="F268" t="n">
+        <v>17.72365040730326</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄欣悦.JPG</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>1.387191456791329</v>
+      </c>
+      <c r="C269" t="n">
+        <v>-1.085687579981921</v>
+      </c>
+      <c r="D269" t="n">
+        <v>-1.444295641437208</v>
+      </c>
+      <c r="E269" t="n">
+        <v>-1.594179480417077</v>
+      </c>
+      <c r="F269" t="n">
+        <v>-5.960958672505152</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄洪秀.JPG</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>0.2262197491686458</v>
+      </c>
+      <c r="C270" t="n">
+        <v>-3.03255268166773</v>
+      </c>
+      <c r="D270" t="n">
+        <v>-1.726928141676632</v>
+      </c>
+      <c r="E270" t="n">
+        <v>-8.31627893298864</v>
+      </c>
+      <c r="F270" t="n">
+        <v>18.16661008961442</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄瑾乔.JPG</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>1.194619362924552</v>
+      </c>
+      <c r="C271" t="n">
+        <v>1.982565131857922</v>
+      </c>
+      <c r="D271" t="n">
+        <v>1.65638707007383</v>
+      </c>
+      <c r="E271" t="n">
+        <v>26.47811542471577</v>
+      </c>
+      <c r="F271" t="n">
+        <v>15.12371642621102</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄真.JPG</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>-0.9721445233945804</v>
+      </c>
+      <c r="C272" t="n">
+        <v>-2.47332405200015</v>
+      </c>
+      <c r="D272" t="n">
+        <v>-2.397320688666333</v>
+      </c>
+      <c r="E272" t="n">
+        <v>6.741858186580473</v>
+      </c>
+      <c r="F272" t="n">
+        <v>3.503001159930394</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄箐.JPG</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>-1.235975720446579</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0.5856328520627639</v>
+      </c>
+      <c r="D273" t="n">
+        <v>1.963013695978701</v>
+      </c>
+      <c r="E273" t="n">
+        <v>-2.380536295102819</v>
+      </c>
+      <c r="F273" t="n">
+        <v>-5.059231116708773</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄纯.JPG</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>1.288895762830298</v>
+      </c>
+      <c r="C274" t="n">
+        <v>-1.475660895486655</v>
+      </c>
+      <c r="D274" t="n">
+        <v>0.5714462394391064</v>
+      </c>
+      <c r="E274" t="n">
+        <v>-8.960731085588803</v>
+      </c>
+      <c r="F274" t="n">
+        <v>-1.026879938743928</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄耕宁.JPG</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>-1.525059613652361</v>
+      </c>
+      <c r="C275" t="n">
+        <v>-2.037602461125128</v>
+      </c>
+      <c r="D275" t="n">
+        <v>-0.5405622228704126</v>
+      </c>
+      <c r="E275" t="n">
+        <v>-8.207509940280525</v>
+      </c>
+      <c r="F275" t="n">
+        <v>-4.122195679621449</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄良晴.JPG</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>2.111765782429751</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0.6389825714039772</v>
+      </c>
+      <c r="D276" t="n">
+        <v>-0.09384656726320968</v>
+      </c>
+      <c r="E276" t="n">
+        <v>18.63115180951825</v>
+      </c>
+      <c r="F276" t="n">
+        <v>-2.499316846972242</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄芝霖.JPG</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>-0.4852515967628184</v>
+      </c>
+      <c r="C277" t="n">
+        <v>-1.658065286376722</v>
+      </c>
+      <c r="D277" t="n">
+        <v>1.697184028025893</v>
+      </c>
+      <c r="E277" t="n">
+        <v>-7.781155821743207</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0.4485254259734962</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄莞淳.JPG</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>1.411206418347951</v>
+      </c>
+      <c r="C278" t="n">
+        <v>3.744656024079014</v>
+      </c>
+      <c r="D278" t="n">
+        <v>-2.002514964079913</v>
+      </c>
+      <c r="E278" t="n">
+        <v>-4.537100367078691</v>
+      </c>
+      <c r="F278" t="n">
+        <v>12.89915630451492</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄诗航.JPG</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>1.804145281127519</v>
+      </c>
+      <c r="C279" t="n">
+        <v>-0.7745357362182604</v>
+      </c>
+      <c r="D279" t="n">
+        <v>-0.7051689650250409</v>
+      </c>
+      <c r="E279" t="n">
+        <v>-8.328453988189624</v>
+      </c>
+      <c r="F279" t="n">
+        <v>-3.739749842577982</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄雪梅.JPG</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>-1.628343843656416</v>
+      </c>
+      <c r="C280" t="n">
+        <v>-1.722893378215138</v>
+      </c>
+      <c r="D280" t="n">
+        <v>0.5746482557524585</v>
+      </c>
+      <c r="E280" t="n">
+        <v>-4.740934269379061</v>
+      </c>
+      <c r="F280" t="n">
+        <v>-1.057073348718497</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黄雪瑶.JPG</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>-1.211891386831748</v>
+      </c>
+      <c r="C281" t="n">
+        <v>1.9820800573082</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0.570531242671202</v>
+      </c>
+      <c r="E281" t="n">
+        <v>-2.843726965281709</v>
+      </c>
+      <c r="F281" t="n">
+        <v>-9.159089532082612</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/黎火金.JPG</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>-0.277678414610771</v>
+      </c>
+      <c r="C282" t="n">
+        <v>-0.4949630447197959</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0.7969597972596052</v>
+      </c>
+      <c r="E282" t="n">
+        <v>-0.354437798002723</v>
+      </c>
+      <c r="F282" t="n">
+        <v>-0.05697712414304284</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/龚圣华.JPG</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>-0.2662527481955085</v>
+      </c>
+      <c r="C283" t="n">
+        <v>0.7890075815111662</v>
+      </c>
+      <c r="D283" t="n">
+        <v>0.4592827874738172</v>
+      </c>
+      <c r="E283" t="n">
+        <v>-3.93143289905408</v>
+      </c>
+      <c r="F283" t="n">
+        <v>12.63146536071443</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2. 对称轴157张/龚必东.JPG</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>1.664464606836389</v>
+      </c>
+      <c r="C284" t="n">
+        <v>0.2795323400427868</v>
+      </c>
+      <c r="D284" t="n">
+        <v>-0.6024018189291516</v>
+      </c>
+      <c r="E284" t="n">
+        <v>-6.107119697082482</v>
+      </c>
+      <c r="F284" t="n">
+        <v>6.165927984915696</v>
       </c>
     </row>
   </sheetData>
